--- a/Projects/rfa/drafts/プロジェクト情報申請書_FY26_RFA_事業計画.xlsx
+++ b/Projects/rfa/drafts/プロジェクト情報申請書_FY26_RFA_事業計画.xlsx
@@ -4405,7 +4405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:X67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.625" defaultRowHeight="15.75"/>
   <cols>
     <col width="8.625" customWidth="1" style="18" min="1" max="1"/>
@@ -6491,392 +6491,398 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="125" t="inlineStr">
-        <is>
-          <t>工数合計</t>
-        </is>
-      </c>
-      <c r="C41" s="165" t="n"/>
-      <c r="D41" s="102">
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>（追加④）PoC現場対応</t>
+        </is>
+      </c>
+      <c r="D41" s="0">
         <f>SUM(E41:P41)</f>
         <v/>
       </c>
-      <c r="E41" s="90">
-        <f>SUM(E31:E40)</f>
-        <v/>
-      </c>
-      <c r="F41" s="90">
-        <f>SUM(F31:F40)</f>
-        <v/>
-      </c>
-      <c r="G41" s="90">
-        <f>SUM(G31:G40)</f>
-        <v/>
-      </c>
-      <c r="H41" s="90">
-        <f>SUM(H31:H40)</f>
-        <v/>
-      </c>
-      <c r="I41" s="90">
-        <f>SUM(I31:I40)</f>
-        <v/>
-      </c>
-      <c r="J41" s="90">
-        <f>SUM(J31:J40)</f>
-        <v/>
-      </c>
-      <c r="K41" s="90">
-        <f>SUM(K31:K40)</f>
-        <v/>
-      </c>
-      <c r="L41" s="90">
-        <f>SUM(L31:L40)</f>
-        <v/>
-      </c>
-      <c r="M41" s="90">
-        <f>SUM(M31:M40)</f>
-        <v/>
-      </c>
-      <c r="N41" s="90">
-        <f>SUM(N31:N40)</f>
-        <v/>
-      </c>
-      <c r="O41" s="90">
-        <f>SUM(O31:O40)</f>
-        <v/>
-      </c>
-      <c r="P41" s="90">
-        <f>SUM(P31:P40)</f>
-        <v/>
-      </c>
-      <c r="Q41" s="24" t="n"/>
-      <c r="R41" s="89">
-        <f>SUM(E41:G41)</f>
-        <v/>
-      </c>
-      <c r="S41" s="89">
-        <f>SUM(H41:J41)</f>
-        <v/>
-      </c>
-      <c r="T41" s="89">
-        <f>SUM(K41:M41)</f>
-        <v/>
-      </c>
-      <c r="U41" s="89">
-        <f>SUM(N41:P41)</f>
-        <v/>
-      </c>
-      <c r="V41" s="90">
-        <f>SUM(R41:U41)</f>
-        <v/>
+      <c r="E41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="125" t="inlineStr">
         <is>
+          <t>工数合計</t>
+        </is>
+      </c>
+      <c r="C42" s="165" t="n"/>
+      <c r="D42" s="102">
+        <f>SUM(D31:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="90">
+        <f>SUM(E31:E41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="90">
+        <f>SUM(F31:F41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="90">
+        <f>SUM(G31:G41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="90">
+        <f>SUM(H31:H41)</f>
+        <v/>
+      </c>
+      <c r="I42" s="90">
+        <f>SUM(I31:I41)</f>
+        <v/>
+      </c>
+      <c r="J42" s="90">
+        <f>SUM(J31:J41)</f>
+        <v/>
+      </c>
+      <c r="K42" s="90">
+        <f>SUM(K31:K41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="90">
+        <f>SUM(L31:L41)</f>
+        <v/>
+      </c>
+      <c r="M42" s="90">
+        <f>SUM(M31:M41)</f>
+        <v/>
+      </c>
+      <c r="N42" s="90">
+        <f>SUM(N31:N41)</f>
+        <v/>
+      </c>
+      <c r="O42" s="90">
+        <f>SUM(O31:O41)</f>
+        <v/>
+      </c>
+      <c r="P42" s="90">
+        <f>SUM(P31:P41)</f>
+        <v/>
+      </c>
+      <c r="Q42" s="24" t="n"/>
+      <c r="R42" s="89">
+        <f>SUM(E41:G41)</f>
+        <v/>
+      </c>
+      <c r="S42" s="89">
+        <f>SUM(H41:J41)</f>
+        <v/>
+      </c>
+      <c r="T42" s="89">
+        <f>SUM(K41:M41)</f>
+        <v/>
+      </c>
+      <c r="U42" s="89">
+        <f>SUM(N41:P41)</f>
+        <v/>
+      </c>
+      <c r="V42" s="90">
+        <f>SUM(R41:U41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="125" t="inlineStr">
+        <is>
           <t>金額合計（原価レート106万円）</t>
         </is>
       </c>
-      <c r="C42" s="165" t="n"/>
-      <c r="D42" s="88">
-        <f>D41*1060000</f>
-        <v/>
-      </c>
-      <c r="E42" s="88">
-        <f>E41*1060000</f>
-        <v/>
-      </c>
-      <c r="F42" s="88">
-        <f>F41*1060000</f>
-        <v/>
-      </c>
-      <c r="G42" s="88">
-        <f>G41*1060000</f>
-        <v/>
-      </c>
-      <c r="H42" s="88">
-        <f>H41*1060000</f>
-        <v/>
-      </c>
-      <c r="I42" s="88">
-        <f>I41*1060000</f>
-        <v/>
-      </c>
-      <c r="J42" s="88">
-        <f>J41*1060000</f>
-        <v/>
-      </c>
-      <c r="K42" s="88">
-        <f>K41*1060000</f>
-        <v/>
-      </c>
-      <c r="L42" s="88">
-        <f>L41*1060000</f>
-        <v/>
-      </c>
-      <c r="M42" s="88">
-        <f>M41*1060000</f>
-        <v/>
-      </c>
-      <c r="N42" s="88">
-        <f>N41*1060000</f>
-        <v/>
-      </c>
-      <c r="O42" s="88">
-        <f>O41*1060000</f>
-        <v/>
-      </c>
-      <c r="P42" s="88">
-        <f>P41*1060000</f>
-        <v/>
-      </c>
-      <c r="Q42" s="18" t="n"/>
-      <c r="R42" s="88">
+      <c r="C43" s="165" t="n"/>
+      <c r="D43" s="88">
+        <f>D42*1060000</f>
+        <v/>
+      </c>
+      <c r="E43" s="88">
+        <f>E42*1060000</f>
+        <v/>
+      </c>
+      <c r="F43" s="88">
+        <f>F42*1060000</f>
+        <v/>
+      </c>
+      <c r="G43" s="88">
+        <f>G42*1060000</f>
+        <v/>
+      </c>
+      <c r="H43" s="88">
+        <f>H42*1060000</f>
+        <v/>
+      </c>
+      <c r="I43" s="88">
+        <f>I42*1060000</f>
+        <v/>
+      </c>
+      <c r="J43" s="88">
+        <f>J42*1060000</f>
+        <v/>
+      </c>
+      <c r="K43" s="88">
+        <f>K42*1060000</f>
+        <v/>
+      </c>
+      <c r="L43" s="88">
+        <f>L42*1060000</f>
+        <v/>
+      </c>
+      <c r="M43" s="88">
+        <f>M42*1060000</f>
+        <v/>
+      </c>
+      <c r="N43" s="88">
+        <f>N42*1060000</f>
+        <v/>
+      </c>
+      <c r="O43" s="88">
+        <f>O42*1060000</f>
+        <v/>
+      </c>
+      <c r="P43" s="88">
+        <f>P42*1060000</f>
+        <v/>
+      </c>
+      <c r="Q43" s="18" t="n"/>
+      <c r="R43" s="88">
         <f>R41*1060000</f>
         <v/>
       </c>
-      <c r="S42" s="88">
+      <c r="S43" s="88">
         <f>S41*1060000</f>
         <v/>
       </c>
-      <c r="T42" s="88">
+      <c r="T43" s="88">
         <f>T41*1060000</f>
         <v/>
       </c>
-      <c r="U42" s="88">
+      <c r="U43" s="88">
         <f>U41*1060000</f>
         <v/>
       </c>
-      <c r="V42" s="88">
+      <c r="V43" s="88">
         <f>SUM(R42:U42)</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="Q43" s="18" t="n"/>
-    </row>
     <row r="44">
-      <c r="B44" s="111" t="inlineStr">
+      <c r="Q44" s="18" t="n"/>
+    </row>
+    <row r="45" ht="29.1" customHeight="1" s="154">
+      <c r="B45" s="111" t="inlineStr">
         <is>
           <t>CEC費用負担分</t>
         </is>
       </c>
-      <c r="C44" s="112" t="n"/>
-      <c r="D44" s="127" t="inlineStr">
+      <c r="C45" s="112" t="n"/>
+      <c r="D45" s="127" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="E44" s="128" t="inlineStr">
+      <c r="E45" s="128" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="F44" s="128" t="inlineStr">
+      <c r="F45" s="128" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="G44" s="128" t="inlineStr">
+      <c r="G45" s="128" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H44" s="128" t="inlineStr">
+      <c r="H45" s="128" t="inlineStr">
         <is>
           <t>７月</t>
         </is>
       </c>
-      <c r="I44" s="128" t="inlineStr">
+      <c r="I45" s="128" t="inlineStr">
         <is>
           <t>８月</t>
         </is>
       </c>
-      <c r="J44" s="128" t="inlineStr">
+      <c r="J45" s="128" t="inlineStr">
         <is>
           <t>９月</t>
         </is>
       </c>
-      <c r="K44" s="128" t="inlineStr">
+      <c r="K45" s="128" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="L44" s="128" t="inlineStr">
+      <c r="L45" s="128" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="M44" s="128" t="inlineStr">
+      <c r="M45" s="128" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="N44" s="128" t="inlineStr">
+      <c r="N45" s="128" t="inlineStr">
         <is>
           <t>１月</t>
         </is>
       </c>
-      <c r="O44" s="128" t="inlineStr">
+      <c r="O45" s="128" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="P44" s="129" t="inlineStr">
+      <c r="P45" s="129" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="Q44" s="19" t="n"/>
-      <c r="R44" s="129" t="inlineStr">
+      <c r="Q45" s="19" t="n"/>
+      <c r="R45" s="129" t="inlineStr">
         <is>
           <t>１Q計画</t>
         </is>
       </c>
-      <c r="S44" s="130" t="inlineStr">
+      <c r="S45" s="130" t="inlineStr">
         <is>
           <t>２Q計画</t>
         </is>
       </c>
-      <c r="T44" s="130" t="inlineStr">
+      <c r="T45" s="130" t="inlineStr">
         <is>
           <t>３Q計画</t>
         </is>
       </c>
-      <c r="U44" s="130" t="inlineStr">
+      <c r="U45" s="130" t="inlineStr">
         <is>
           <t>4Q計画</t>
         </is>
       </c>
-      <c r="V44" s="130" t="inlineStr">
+      <c r="V45" s="130" t="inlineStr">
         <is>
           <t>合計計画</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="29.1" customHeight="1" s="154">
-      <c r="B45" s="113" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="113" t="inlineStr">
         <is>
           <t>＜経費＞</t>
         </is>
       </c>
-      <c r="C45" s="93" t="inlineStr">
+      <c r="C46" s="93" t="inlineStr">
         <is>
           <t>明細</t>
         </is>
       </c>
-      <c r="D45" s="100">
+      <c r="D46" s="100">
         <f>SUM(E45:P45)</f>
         <v/>
       </c>
-      <c r="E45" s="93">
+      <c r="E46" s="93">
         <f>SUM(E46:E49)</f>
         <v/>
       </c>
-      <c r="F45" s="93">
+      <c r="F46" s="93">
         <f>SUM(F46:F49)</f>
         <v/>
       </c>
-      <c r="G45" s="93">
+      <c r="G46" s="93">
         <f>SUM(G46:G49)</f>
         <v/>
       </c>
-      <c r="H45" s="93">
+      <c r="H46" s="93">
         <f>SUM(H46:H49)</f>
         <v/>
       </c>
-      <c r="I45" s="93">
+      <c r="I46" s="93">
         <f>SUM(I46:I49)</f>
         <v/>
       </c>
-      <c r="J45" s="93">
+      <c r="J46" s="93">
         <f>SUM(J46:J49)</f>
         <v/>
       </c>
-      <c r="K45" s="93">
+      <c r="K46" s="93">
         <f>SUM(K46:K49)</f>
         <v/>
       </c>
-      <c r="L45" s="93">
+      <c r="L46" s="93">
         <f>SUM(L46:L49)</f>
         <v/>
       </c>
-      <c r="M45" s="93">
+      <c r="M46" s="93">
         <f>SUM(M46:M49)</f>
         <v/>
       </c>
-      <c r="N45" s="93">
+      <c r="N46" s="93">
         <f>SUM(N46:N49)</f>
         <v/>
       </c>
-      <c r="O45" s="93">
+      <c r="O46" s="93">
         <f>SUM(O46:O49)</f>
         <v/>
       </c>
-      <c r="P45" s="93">
+      <c r="P46" s="93">
         <f>SUM(P46:P49)</f>
         <v/>
       </c>
-      <c r="Q45" s="18" t="n"/>
-      <c r="R45" s="93">
-        <f>SUM(E45:G45)</f>
-        <v/>
-      </c>
-      <c r="S45" s="94">
-        <f>SUM(H45:J45)</f>
-        <v/>
-      </c>
-      <c r="T45" s="93">
-        <f>SUM(K45:M45)</f>
-        <v/>
-      </c>
-      <c r="U45" s="93">
-        <f>SUM(N45:P45)</f>
-        <v/>
-      </c>
-      <c r="V45" s="93">
-        <f>SUM(R45:U45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="20" t="n"/>
-      <c r="C46" s="39" t="n"/>
-      <c r="D46" s="93">
-        <f>SUM(E46:P46)</f>
-        <v/>
-      </c>
-      <c r="E46" s="39" t="n"/>
-      <c r="F46" s="39" t="n"/>
-      <c r="G46" s="39" t="n"/>
-      <c r="H46" s="39" t="n"/>
-      <c r="I46" s="39" t="n"/>
-      <c r="J46" s="39" t="n"/>
-      <c r="K46" s="39" t="n"/>
-      <c r="L46" s="39" t="n"/>
-      <c r="M46" s="39" t="n"/>
-      <c r="N46" s="39" t="n"/>
-      <c r="O46" s="39" t="n"/>
-      <c r="P46" s="39" t="n"/>
       <c r="Q46" s="18" t="n"/>
       <c r="R46" s="93">
-        <f>SUM(E46:G46)</f>
+        <f>SUM(E45:G45)</f>
         <v/>
       </c>
       <c r="S46" s="94">
-        <f>SUM(H46:J46)</f>
+        <f>SUM(H45:J45)</f>
         <v/>
       </c>
       <c r="T46" s="93">
-        <f>SUM(K46:M46)</f>
+        <f>SUM(K45:M45)</f>
         <v/>
       </c>
       <c r="U46" s="93">
-        <f>SUM(N46:P46)</f>
+        <f>SUM(N45:P45)</f>
         <v/>
       </c>
       <c r="V46" s="93">
-        <f>SUM(R46:U46)</f>
+        <f>SUM(R45:U45)</f>
         <v/>
       </c>
     </row>
@@ -6884,7 +6890,7 @@
       <c r="B47" s="20" t="n"/>
       <c r="C47" s="39" t="n"/>
       <c r="D47" s="93">
-        <f>SUM(E47:P47)</f>
+        <f>SUM(E46:P46)</f>
         <v/>
       </c>
       <c r="E47" s="39" t="n"/>
@@ -6901,23 +6907,23 @@
       <c r="P47" s="39" t="n"/>
       <c r="Q47" s="18" t="n"/>
       <c r="R47" s="93">
-        <f>SUM(E47:G47)</f>
+        <f>SUM(E46:G46)</f>
         <v/>
       </c>
       <c r="S47" s="94">
-        <f>SUM(H47:J47)</f>
+        <f>SUM(H46:J46)</f>
         <v/>
       </c>
       <c r="T47" s="93">
-        <f>SUM(K47:M47)</f>
+        <f>SUM(K46:M46)</f>
         <v/>
       </c>
       <c r="U47" s="93">
-        <f>SUM(N47:P47)</f>
+        <f>SUM(N46:P46)</f>
         <v/>
       </c>
       <c r="V47" s="93">
-        <f>SUM(R47:U47)</f>
+        <f>SUM(R46:U46)</f>
         <v/>
       </c>
     </row>
@@ -6925,7 +6931,7 @@
       <c r="B48" s="20" t="n"/>
       <c r="C48" s="39" t="n"/>
       <c r="D48" s="93">
-        <f>SUM(E48:P48)</f>
+        <f>SUM(E47:P47)</f>
         <v/>
       </c>
       <c r="E48" s="39" t="n"/>
@@ -6942,23 +6948,23 @@
       <c r="P48" s="39" t="n"/>
       <c r="Q48" s="18" t="n"/>
       <c r="R48" s="93">
-        <f>SUM(E48:G48)</f>
+        <f>SUM(E47:G47)</f>
         <v/>
       </c>
       <c r="S48" s="94">
-        <f>SUM(H48:J48)</f>
+        <f>SUM(H47:J47)</f>
         <v/>
       </c>
       <c r="T48" s="93">
-        <f>SUM(K48:M48)</f>
+        <f>SUM(K47:M47)</f>
         <v/>
       </c>
       <c r="U48" s="93">
-        <f>SUM(N48:P48)</f>
+        <f>SUM(N47:P47)</f>
         <v/>
       </c>
       <c r="V48" s="93">
-        <f>SUM(R48:U48)</f>
+        <f>SUM(R47:U47)</f>
         <v/>
       </c>
     </row>
@@ -6966,7 +6972,7 @@
       <c r="B49" s="20" t="n"/>
       <c r="C49" s="39" t="n"/>
       <c r="D49" s="93">
-        <f>SUM(E49:P49)</f>
+        <f>SUM(E48:P48)</f>
         <v/>
       </c>
       <c r="E49" s="39" t="n"/>
@@ -6983,265 +6989,265 @@
       <c r="P49" s="39" t="n"/>
       <c r="Q49" s="18" t="n"/>
       <c r="R49" s="93">
+        <f>SUM(E48:G48)</f>
+        <v/>
+      </c>
+      <c r="S49" s="94">
+        <f>SUM(H48:J48)</f>
+        <v/>
+      </c>
+      <c r="T49" s="93">
+        <f>SUM(K48:M48)</f>
+        <v/>
+      </c>
+      <c r="U49" s="93">
+        <f>SUM(N48:P48)</f>
+        <v/>
+      </c>
+      <c r="V49" s="93">
+        <f>SUM(R48:U48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="20" t="n"/>
+      <c r="C50" s="39" t="n"/>
+      <c r="D50" s="93">
+        <f>SUM(E49:P49)</f>
+        <v/>
+      </c>
+      <c r="E50" s="39" t="n"/>
+      <c r="F50" s="39" t="n"/>
+      <c r="G50" s="39" t="n"/>
+      <c r="H50" s="39" t="n"/>
+      <c r="I50" s="39" t="n"/>
+      <c r="J50" s="39" t="n"/>
+      <c r="K50" s="39" t="n"/>
+      <c r="L50" s="39" t="n"/>
+      <c r="M50" s="39" t="n"/>
+      <c r="N50" s="39" t="n"/>
+      <c r="O50" s="39" t="n"/>
+      <c r="P50" s="39" t="n"/>
+      <c r="Q50" s="18" t="n"/>
+      <c r="R50" s="93">
         <f>SUM(E49:G49)</f>
         <v/>
       </c>
-      <c r="S49" s="94">
+      <c r="S50" s="94">
         <f>SUM(H49:J49)</f>
         <v/>
       </c>
-      <c r="T49" s="93">
+      <c r="T50" s="93">
         <f>SUM(K49:M49)</f>
         <v/>
       </c>
-      <c r="U49" s="93">
+      <c r="U50" s="93">
         <f>SUM(N49:P49)</f>
         <v/>
       </c>
-      <c r="V49" s="93">
+      <c r="V50" s="93">
         <f>SUM(R49:U49)</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="D50" s="47" t="n"/>
-      <c r="Q50" s="18" t="n"/>
-      <c r="R50" s="46" t="n"/>
-    </row>
     <row r="51">
-      <c r="B51" s="111" t="inlineStr">
+      <c r="D51" s="47" t="n"/>
+      <c r="Q51" s="18" t="n"/>
+      <c r="R51" s="46" t="n"/>
+    </row>
+    <row r="52" ht="29.1" customHeight="1" s="154">
+      <c r="B52" s="111" t="inlineStr">
         <is>
           <t>海外研人件費　＊個別委託契約は、経費の研究費計上</t>
         </is>
       </c>
-      <c r="C51" s="112" t="n"/>
-      <c r="D51" s="127" t="inlineStr">
+      <c r="C52" s="112" t="n"/>
+      <c r="D52" s="127" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="E51" s="128" t="inlineStr">
+      <c r="E52" s="128" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="F51" s="128" t="inlineStr">
+      <c r="F52" s="128" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="G51" s="128" t="inlineStr">
+      <c r="G52" s="128" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H51" s="128" t="inlineStr">
+      <c r="H52" s="128" t="inlineStr">
         <is>
           <t>７月</t>
         </is>
       </c>
-      <c r="I51" s="128" t="inlineStr">
+      <c r="I52" s="128" t="inlineStr">
         <is>
           <t>８月</t>
         </is>
       </c>
-      <c r="J51" s="128" t="inlineStr">
+      <c r="J52" s="128" t="inlineStr">
         <is>
           <t>９月</t>
         </is>
       </c>
-      <c r="K51" s="128" t="inlineStr">
+      <c r="K52" s="128" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="L51" s="128" t="inlineStr">
+      <c r="L52" s="128" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="M51" s="128" t="inlineStr">
+      <c r="M52" s="128" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="N51" s="128" t="inlineStr">
+      <c r="N52" s="128" t="inlineStr">
         <is>
           <t>１月</t>
         </is>
       </c>
-      <c r="O51" s="128" t="inlineStr">
+      <c r="O52" s="128" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="P51" s="129" t="inlineStr">
+      <c r="P52" s="129" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="Q51" s="19" t="n"/>
-      <c r="R51" s="129" t="inlineStr">
+      <c r="Q52" s="19" t="n"/>
+      <c r="R52" s="129" t="inlineStr">
         <is>
           <t>１Q計画</t>
         </is>
       </c>
-      <c r="S51" s="130" t="inlineStr">
+      <c r="S52" s="130" t="inlineStr">
         <is>
           <t>２Q計画</t>
         </is>
       </c>
-      <c r="T51" s="130" t="inlineStr">
+      <c r="T52" s="130" t="inlineStr">
         <is>
           <t>３Q計画</t>
         </is>
       </c>
-      <c r="U51" s="130" t="inlineStr">
+      <c r="U52" s="130" t="inlineStr">
         <is>
           <t>4Q計画</t>
         </is>
       </c>
-      <c r="V51" s="130" t="inlineStr">
+      <c r="V52" s="130" t="inlineStr">
         <is>
           <t>合計計画</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="29.1" customHeight="1" s="154">
-      <c r="B52" s="113" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="113" t="inlineStr">
         <is>
           <t>＜経費＞</t>
         </is>
       </c>
-      <c r="C52" s="93" t="inlineStr">
+      <c r="C53" s="93" t="inlineStr">
         <is>
           <t>明細</t>
         </is>
       </c>
-      <c r="D52" s="100">
+      <c r="D53" s="100">
         <f>SUM(E52:P52)</f>
         <v/>
       </c>
-      <c r="E52" s="93">
+      <c r="E53" s="93">
         <f>SUM(E53:E56)</f>
         <v/>
       </c>
-      <c r="F52" s="93">
+      <c r="F53" s="93">
         <f>SUM(F53:F56)</f>
         <v/>
       </c>
-      <c r="G52" s="93">
+      <c r="G53" s="93">
         <f>SUM(G53:G56)</f>
         <v/>
       </c>
-      <c r="H52" s="93">
+      <c r="H53" s="93">
         <f>SUM(H53:H56)</f>
         <v/>
       </c>
-      <c r="I52" s="93">
+      <c r="I53" s="93">
         <f>SUM(I53:I56)</f>
         <v/>
       </c>
-      <c r="J52" s="93">
+      <c r="J53" s="93">
         <f>SUM(J53:J56)</f>
         <v/>
       </c>
-      <c r="K52" s="93">
+      <c r="K53" s="93">
         <f>SUM(K53:K56)</f>
         <v/>
       </c>
-      <c r="L52" s="93">
+      <c r="L53" s="93">
         <f>SUM(L53:L56)</f>
         <v/>
       </c>
-      <c r="M52" s="93">
+      <c r="M53" s="93">
         <f>SUM(M53:M56)</f>
         <v/>
       </c>
-      <c r="N52" s="93">
+      <c r="N53" s="93">
         <f>SUM(N53:N56)</f>
         <v/>
       </c>
-      <c r="O52" s="93">
+      <c r="O53" s="93">
         <f>SUM(O53:O56)</f>
         <v/>
       </c>
-      <c r="P52" s="93">
+      <c r="P53" s="93">
         <f>SUM(P53:P56)</f>
         <v/>
       </c>
-      <c r="Q52" s="18" t="n"/>
-      <c r="R52" s="93">
-        <f>SUM(E52:G52)</f>
-        <v/>
-      </c>
-      <c r="S52" s="94">
-        <f>SUM(H52:J52)</f>
-        <v/>
-      </c>
-      <c r="T52" s="93">
-        <f>SUM(K52:M52)</f>
-        <v/>
-      </c>
-      <c r="U52" s="93">
-        <f>SUM(N52:P52)</f>
-        <v/>
-      </c>
-      <c r="V52" s="93">
-        <f>SUM(R52:U52)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="20" t="inlineStr">
-        <is>
-          <t>研究費</t>
-        </is>
-      </c>
-      <c r="C53" s="39" t="n"/>
-      <c r="D53" s="93">
-        <f>SUM(E53:P53)</f>
-        <v/>
-      </c>
-      <c r="E53" s="39" t="n"/>
-      <c r="F53" s="39" t="n"/>
-      <c r="G53" s="39" t="n"/>
-      <c r="H53" s="39" t="n"/>
-      <c r="I53" s="39" t="n"/>
-      <c r="J53" s="39" t="n"/>
-      <c r="K53" s="39" t="n"/>
-      <c r="L53" s="39" t="n"/>
-      <c r="M53" s="39" t="n"/>
-      <c r="N53" s="39" t="n"/>
-      <c r="O53" s="39" t="n"/>
-      <c r="P53" s="39" t="n"/>
       <c r="Q53" s="18" t="n"/>
       <c r="R53" s="93">
-        <f>SUM(E53:G53)</f>
+        <f>SUM(E52:G52)</f>
         <v/>
       </c>
       <c r="S53" s="94">
-        <f>SUM(H53:J53)</f>
+        <f>SUM(H52:J52)</f>
         <v/>
       </c>
       <c r="T53" s="93">
-        <f>SUM(K53:M53)</f>
+        <f>SUM(K52:M52)</f>
         <v/>
       </c>
       <c r="U53" s="93">
-        <f>SUM(N53:P53)</f>
+        <f>SUM(N52:P52)</f>
         <v/>
       </c>
       <c r="V53" s="93">
-        <f>SUM(R53:U53)</f>
+        <f>SUM(R52:U52)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="20" t="n"/>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>研究費</t>
+        </is>
+      </c>
       <c r="C54" s="39" t="n"/>
       <c r="D54" s="93">
-        <f>SUM(E54:P54)</f>
+        <f>SUM(E53:P53)</f>
         <v/>
       </c>
       <c r="E54" s="39" t="n"/>
@@ -7258,23 +7264,23 @@
       <c r="P54" s="39" t="n"/>
       <c r="Q54" s="18" t="n"/>
       <c r="R54" s="93">
-        <f>SUM(E54:G54)</f>
+        <f>SUM(E53:G53)</f>
         <v/>
       </c>
       <c r="S54" s="94">
-        <f>SUM(H54:J54)</f>
+        <f>SUM(H53:J53)</f>
         <v/>
       </c>
       <c r="T54" s="93">
-        <f>SUM(K54:M54)</f>
+        <f>SUM(K53:M53)</f>
         <v/>
       </c>
       <c r="U54" s="93">
-        <f>SUM(N54:P54)</f>
+        <f>SUM(N53:P53)</f>
         <v/>
       </c>
       <c r="V54" s="93">
-        <f>SUM(R54:U54)</f>
+        <f>SUM(R53:U53)</f>
         <v/>
       </c>
     </row>
@@ -7282,7 +7288,7 @@
       <c r="B55" s="20" t="n"/>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="93">
-        <f>SUM(E55:P55)</f>
+        <f>SUM(E54:P54)</f>
         <v/>
       </c>
       <c r="E55" s="39" t="n"/>
@@ -7299,23 +7305,23 @@
       <c r="P55" s="39" t="n"/>
       <c r="Q55" s="18" t="n"/>
       <c r="R55" s="93">
-        <f>SUM(E55:G55)</f>
+        <f>SUM(E54:G54)</f>
         <v/>
       </c>
       <c r="S55" s="94">
-        <f>SUM(H55:J55)</f>
+        <f>SUM(H54:J54)</f>
         <v/>
       </c>
       <c r="T55" s="93">
-        <f>SUM(K55:M55)</f>
+        <f>SUM(K54:M54)</f>
         <v/>
       </c>
       <c r="U55" s="93">
-        <f>SUM(N55:P55)</f>
+        <f>SUM(N54:P54)</f>
         <v/>
       </c>
       <c r="V55" s="93">
-        <f>SUM(R55:U55)</f>
+        <f>SUM(R54:U54)</f>
         <v/>
       </c>
     </row>
@@ -7323,7 +7329,7 @@
       <c r="B56" s="20" t="n"/>
       <c r="C56" s="39" t="n"/>
       <c r="D56" s="93">
-        <f>SUM(E56:P56)</f>
+        <f>SUM(E55:P55)</f>
         <v/>
       </c>
       <c r="E56" s="39" t="n"/>
@@ -7340,260 +7346,261 @@
       <c r="P56" s="39" t="n"/>
       <c r="Q56" s="18" t="n"/>
       <c r="R56" s="93">
+        <f>SUM(E55:G55)</f>
+        <v/>
+      </c>
+      <c r="S56" s="94">
+        <f>SUM(H55:J55)</f>
+        <v/>
+      </c>
+      <c r="T56" s="93">
+        <f>SUM(K55:M55)</f>
+        <v/>
+      </c>
+      <c r="U56" s="93">
+        <f>SUM(N55:P55)</f>
+        <v/>
+      </c>
+      <c r="V56" s="93">
+        <f>SUM(R55:U55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="39" t="n"/>
+      <c r="D57" s="93">
+        <f>SUM(E56:P56)</f>
+        <v/>
+      </c>
+      <c r="E57" s="39" t="n"/>
+      <c r="F57" s="39" t="n"/>
+      <c r="G57" s="39" t="n"/>
+      <c r="H57" s="39" t="n"/>
+      <c r="I57" s="39" t="n"/>
+      <c r="J57" s="39" t="n"/>
+      <c r="K57" s="39" t="n"/>
+      <c r="L57" s="39" t="n"/>
+      <c r="M57" s="39" t="n"/>
+      <c r="N57" s="39" t="n"/>
+      <c r="O57" s="39" t="n"/>
+      <c r="P57" s="39" t="n"/>
+      <c r="Q57" s="18" t="n"/>
+      <c r="R57" s="93">
         <f>SUM(E56:G56)</f>
         <v/>
       </c>
-      <c r="S56" s="94">
+      <c r="S57" s="94">
         <f>SUM(H56:J56)</f>
         <v/>
       </c>
-      <c r="T56" s="93">
+      <c r="T57" s="93">
         <f>SUM(K56:M56)</f>
         <v/>
       </c>
-      <c r="U56" s="93">
+      <c r="U57" s="93">
         <f>SUM(N56:P56)</f>
         <v/>
       </c>
-      <c r="V56" s="93">
+      <c r="V57" s="93">
         <f>SUM(R56:U56)</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1" s="154">
-      <c r="B58" s="166" t="inlineStr">
+    <row r="58" ht="30" customHeight="1" s="154"/>
+    <row r="59">
+      <c r="B59" s="166" t="inlineStr">
         <is>
           <t>設備投資（固定資産購入を検討している場合は、購入金額をこちらに記載）</t>
         </is>
       </c>
-      <c r="C58" s="165" t="n"/>
-      <c r="D58" s="131" t="inlineStr">
+      <c r="C59" s="165" t="n"/>
+      <c r="D59" s="131" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="E58" s="132" t="inlineStr">
+      <c r="E59" s="132" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="F58" s="132" t="inlineStr">
+      <c r="F59" s="132" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="G58" s="132" t="inlineStr">
+      <c r="G59" s="132" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H58" s="132" t="inlineStr">
+      <c r="H59" s="132" t="inlineStr">
         <is>
           <t>７月</t>
         </is>
       </c>
-      <c r="I58" s="132" t="inlineStr">
+      <c r="I59" s="132" t="inlineStr">
         <is>
           <t>８月</t>
         </is>
       </c>
-      <c r="J58" s="132" t="inlineStr">
+      <c r="J59" s="132" t="inlineStr">
         <is>
           <t>９月</t>
         </is>
       </c>
-      <c r="K58" s="132" t="inlineStr">
+      <c r="K59" s="132" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="L58" s="132" t="inlineStr">
+      <c r="L59" s="132" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="M58" s="132" t="inlineStr">
+      <c r="M59" s="132" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="N58" s="132" t="inlineStr">
+      <c r="N59" s="132" t="inlineStr">
         <is>
           <t>１月</t>
         </is>
       </c>
-      <c r="O58" s="132" t="inlineStr">
+      <c r="O59" s="132" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="P58" s="132" t="inlineStr">
+      <c r="P59" s="132" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="Q58" s="19" t="n"/>
-      <c r="R58" s="132" t="inlineStr">
+      <c r="Q59" s="19" t="n"/>
+      <c r="R59" s="132" t="inlineStr">
         <is>
           <t>１Q計画</t>
         </is>
       </c>
-      <c r="S58" s="134" t="inlineStr">
+      <c r="S59" s="134" t="inlineStr">
         <is>
           <t>２Q計画</t>
         </is>
       </c>
-      <c r="T58" s="132" t="inlineStr">
+      <c r="T59" s="132" t="inlineStr">
         <is>
           <t>３Q計画</t>
         </is>
       </c>
-      <c r="U58" s="132" t="inlineStr">
+      <c r="U59" s="132" t="inlineStr">
         <is>
           <t>4Q計画</t>
         </is>
       </c>
-      <c r="V58" s="132" t="inlineStr">
+      <c r="V59" s="132" t="inlineStr">
         <is>
           <t>合計計画</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="133" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="133" t="inlineStr">
         <is>
           <t>＜経費＞</t>
         </is>
       </c>
-      <c r="C59" s="97" t="inlineStr">
+      <c r="C60" s="97" t="inlineStr">
         <is>
           <t>明細</t>
         </is>
       </c>
-      <c r="D59" s="99">
+      <c r="D60" s="99">
         <f>SUM(E59:P59)</f>
         <v/>
       </c>
-      <c r="E59" s="97">
+      <c r="E60" s="97">
         <f>SUM(E60:E64)</f>
         <v/>
       </c>
-      <c r="F59" s="97">
+      <c r="F60" s="97">
         <f>SUM(F60:F64)</f>
         <v/>
       </c>
-      <c r="G59" s="97">
+      <c r="G60" s="97">
         <f>SUM(G60:G64)</f>
         <v/>
       </c>
-      <c r="H59" s="97">
+      <c r="H60" s="97">
         <f>SUM(H60:H64)</f>
         <v/>
       </c>
-      <c r="I59" s="97">
+      <c r="I60" s="97">
         <f>SUM(I60:I64)</f>
         <v/>
       </c>
-      <c r="J59" s="97">
+      <c r="J60" s="97">
         <f>SUM(J60:J64)</f>
         <v/>
       </c>
-      <c r="K59" s="97">
+      <c r="K60" s="97">
         <f>SUM(K60:K64)</f>
         <v/>
       </c>
-      <c r="L59" s="97">
+      <c r="L60" s="97">
         <f>SUM(L60:L64)</f>
         <v/>
       </c>
-      <c r="M59" s="97">
+      <c r="M60" s="97">
         <f>SUM(M60:M64)</f>
         <v/>
       </c>
-      <c r="N59" s="97">
+      <c r="N60" s="97">
         <f>SUM(N60:N64)</f>
         <v/>
       </c>
-      <c r="O59" s="97">
+      <c r="O60" s="97">
         <f>SUM(O60:O64)</f>
         <v/>
       </c>
-      <c r="P59" s="97">
+      <c r="P60" s="97">
         <f>SUM(P60:P64)</f>
         <v/>
       </c>
-      <c r="Q59" s="18" t="n"/>
-      <c r="R59" s="97">
-        <f>SUM(E59:G59)</f>
-        <v/>
-      </c>
-      <c r="S59" s="98">
-        <f>SUM(H59:J59)</f>
-        <v/>
-      </c>
-      <c r="T59" s="97">
-        <f>SUM(K59:M59)</f>
-        <v/>
-      </c>
-      <c r="U59" s="97">
-        <f>SUM(N59:P59)</f>
-        <v/>
-      </c>
-      <c r="V59" s="97">
-        <f>SUM(R59:U59)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t>設備購入</t>
-        </is>
-      </c>
-      <c r="C60" s="39" t="n"/>
-      <c r="D60" s="97">
-        <f>SUM(E60:P60)</f>
-        <v/>
-      </c>
-      <c r="E60" s="39" t="n"/>
-      <c r="F60" s="39" t="n"/>
-      <c r="G60" s="39" t="n"/>
-      <c r="H60" s="39" t="n"/>
-      <c r="I60" s="39" t="n"/>
-      <c r="J60" s="39" t="n"/>
-      <c r="K60" s="39" t="n"/>
-      <c r="L60" s="39" t="n"/>
-      <c r="M60" s="39" t="n"/>
-      <c r="N60" s="39" t="n"/>
-      <c r="O60" s="39" t="n"/>
-      <c r="P60" s="39" t="n"/>
       <c r="Q60" s="18" t="n"/>
       <c r="R60" s="97">
-        <f>SUM(E60:G60)</f>
+        <f>SUM(E59:G59)</f>
         <v/>
       </c>
       <c r="S60" s="98">
-        <f>SUM(H60:J60)</f>
+        <f>SUM(H59:J59)</f>
         <v/>
       </c>
       <c r="T60" s="97">
-        <f>SUM(K60:M60)</f>
+        <f>SUM(K59:M59)</f>
         <v/>
       </c>
       <c r="U60" s="97">
-        <f>SUM(N60:P60)</f>
+        <f>SUM(N59:P59)</f>
         <v/>
       </c>
       <c r="V60" s="97">
-        <f>SUM(R60:U60)</f>
+        <f>SUM(R59:U59)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="20" t="n"/>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>設備購入</t>
+        </is>
+      </c>
       <c r="C61" s="39" t="n"/>
       <c r="D61" s="97">
-        <f>SUM(E61:P61)</f>
+        <f>SUM(E60:P60)</f>
         <v/>
       </c>
       <c r="E61" s="39" t="n"/>
@@ -7610,23 +7617,23 @@
       <c r="P61" s="39" t="n"/>
       <c r="Q61" s="18" t="n"/>
       <c r="R61" s="97">
-        <f>SUM(E61:G61)</f>
+        <f>SUM(E60:G60)</f>
         <v/>
       </c>
       <c r="S61" s="98">
-        <f>SUM(H61:J61)</f>
+        <f>SUM(H60:J60)</f>
         <v/>
       </c>
       <c r="T61" s="97">
-        <f>SUM(K61:M61)</f>
+        <f>SUM(K60:M60)</f>
         <v/>
       </c>
       <c r="U61" s="97">
-        <f>SUM(N61:P61)</f>
+        <f>SUM(N60:P60)</f>
         <v/>
       </c>
       <c r="V61" s="97">
-        <f>SUM(R61:U61)</f>
+        <f>SUM(R60:U60)</f>
         <v/>
       </c>
     </row>
@@ -7634,7 +7641,7 @@
       <c r="B62" s="20" t="n"/>
       <c r="C62" s="39" t="n"/>
       <c r="D62" s="97">
-        <f>SUM(E62:P62)</f>
+        <f>SUM(E61:P61)</f>
         <v/>
       </c>
       <c r="E62" s="39" t="n"/>
@@ -7651,23 +7658,23 @@
       <c r="P62" s="39" t="n"/>
       <c r="Q62" s="18" t="n"/>
       <c r="R62" s="97">
-        <f>SUM(E62:G62)</f>
+        <f>SUM(E61:G61)</f>
         <v/>
       </c>
       <c r="S62" s="98">
-        <f>SUM(H62:J62)</f>
+        <f>SUM(H61:J61)</f>
         <v/>
       </c>
       <c r="T62" s="97">
-        <f>SUM(K62:M62)</f>
+        <f>SUM(K61:M61)</f>
         <v/>
       </c>
       <c r="U62" s="97">
-        <f>SUM(N62:P62)</f>
+        <f>SUM(N61:P61)</f>
         <v/>
       </c>
       <c r="V62" s="97">
-        <f>SUM(R62:U62)</f>
+        <f>SUM(R61:U61)</f>
         <v/>
       </c>
     </row>
@@ -7675,7 +7682,7 @@
       <c r="B63" s="20" t="n"/>
       <c r="C63" s="39" t="n"/>
       <c r="D63" s="97">
-        <f>SUM(E63:P63)</f>
+        <f>SUM(E62:P62)</f>
         <v/>
       </c>
       <c r="E63" s="39" t="n"/>
@@ -7692,23 +7699,23 @@
       <c r="P63" s="39" t="n"/>
       <c r="Q63" s="18" t="n"/>
       <c r="R63" s="97">
-        <f>SUM(E63:G63)</f>
+        <f>SUM(E62:G62)</f>
         <v/>
       </c>
       <c r="S63" s="98">
-        <f>SUM(H63:J63)</f>
+        <f>SUM(H62:J62)</f>
         <v/>
       </c>
       <c r="T63" s="97">
-        <f>SUM(K63:M63)</f>
+        <f>SUM(K62:M62)</f>
         <v/>
       </c>
       <c r="U63" s="97">
-        <f>SUM(N63:P63)</f>
+        <f>SUM(N62:P62)</f>
         <v/>
       </c>
       <c r="V63" s="97">
-        <f>SUM(R63:U63)</f>
+        <f>SUM(R62:U62)</f>
         <v/>
       </c>
     </row>
@@ -7716,7 +7723,7 @@
       <c r="B64" s="20" t="n"/>
       <c r="C64" s="39" t="n"/>
       <c r="D64" s="97">
-        <f>SUM(E64:P64)</f>
+        <f>SUM(E63:P63)</f>
         <v/>
       </c>
       <c r="E64" s="39" t="n"/>
@@ -7733,79 +7740,120 @@
       <c r="P64" s="39" t="n"/>
       <c r="Q64" s="18" t="n"/>
       <c r="R64" s="97">
+        <f>SUM(E63:G63)</f>
+        <v/>
+      </c>
+      <c r="S64" s="98">
+        <f>SUM(H63:J63)</f>
+        <v/>
+      </c>
+      <c r="T64" s="97">
+        <f>SUM(K63:M63)</f>
+        <v/>
+      </c>
+      <c r="U64" s="97">
+        <f>SUM(N63:P63)</f>
+        <v/>
+      </c>
+      <c r="V64" s="97">
+        <f>SUM(R63:U63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="20" t="n"/>
+      <c r="C65" s="39" t="n"/>
+      <c r="D65" s="97">
+        <f>SUM(E64:P64)</f>
+        <v/>
+      </c>
+      <c r="E65" s="39" t="n"/>
+      <c r="F65" s="39" t="n"/>
+      <c r="G65" s="39" t="n"/>
+      <c r="H65" s="39" t="n"/>
+      <c r="I65" s="39" t="n"/>
+      <c r="J65" s="39" t="n"/>
+      <c r="K65" s="39" t="n"/>
+      <c r="L65" s="39" t="n"/>
+      <c r="M65" s="39" t="n"/>
+      <c r="N65" s="39" t="n"/>
+      <c r="O65" s="39" t="n"/>
+      <c r="P65" s="39" t="n"/>
+      <c r="Q65" s="18" t="n"/>
+      <c r="R65" s="97">
         <f>SUM(E64:G64)</f>
         <v/>
       </c>
-      <c r="S64" s="98">
+      <c r="S65" s="98">
         <f>SUM(H64:J64)</f>
         <v/>
       </c>
-      <c r="T64" s="97">
+      <c r="T65" s="97">
         <f>SUM(K64:M64)</f>
         <v/>
       </c>
-      <c r="U64" s="97">
+      <c r="U65" s="97">
         <f>SUM(N64:P64)</f>
         <v/>
       </c>
-      <c r="V64" s="97">
+      <c r="V65" s="97">
         <f>SUM(R64:U64)</f>
         <v/>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="110" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="110" t="inlineStr">
         <is>
           <t>例</t>
         </is>
       </c>
-      <c r="B65" s="110" t="inlineStr">
+      <c r="B66" s="110" t="inlineStr">
         <is>
           <t>設備購入</t>
         </is>
       </c>
-      <c r="C65" s="110" t="inlineStr">
+      <c r="C66" s="110" t="inlineStr">
         <is>
           <t>AA装置、3台</t>
         </is>
       </c>
-      <c r="D65" s="110" t="n"/>
-      <c r="E65" s="110" t="n"/>
-      <c r="F65" s="110" t="n"/>
-      <c r="G65" s="110" t="n"/>
-      <c r="H65" s="110" t="n">
+      <c r="D66" s="110" t="n"/>
+      <c r="E66" s="110" t="n"/>
+      <c r="F66" s="110" t="n"/>
+      <c r="G66" s="110" t="n"/>
+      <c r="H66" s="110" t="n">
         <v>5000000</v>
       </c>
-      <c r="I65" s="110" t="n"/>
-      <c r="J65" s="110" t="n"/>
-      <c r="K65" s="53" t="n"/>
-      <c r="L65" s="53" t="n"/>
-      <c r="M65" s="53" t="n"/>
-      <c r="N65" s="53" t="n"/>
-      <c r="O65" s="53" t="n"/>
-      <c r="P65" s="53" t="n"/>
-      <c r="Q65" s="53" t="n"/>
-      <c r="R65" s="53" t="n"/>
-      <c r="S65" s="53" t="n"/>
-      <c r="T65" s="53" t="n"/>
-      <c r="U65" s="53" t="n"/>
-      <c r="V65" s="53" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="121" t="n"/>
-      <c r="B66" s="121" t="inlineStr">
+      <c r="I66" s="110" t="n"/>
+      <c r="J66" s="110" t="n"/>
+      <c r="K66" s="53" t="n"/>
+      <c r="L66" s="53" t="n"/>
+      <c r="M66" s="53" t="n"/>
+      <c r="N66" s="53" t="n"/>
+      <c r="O66" s="53" t="n"/>
+      <c r="P66" s="53" t="n"/>
+      <c r="Q66" s="53" t="n"/>
+      <c r="R66" s="53" t="n"/>
+      <c r="S66" s="53" t="n"/>
+      <c r="T66" s="53" t="n"/>
+      <c r="U66" s="53" t="n"/>
+      <c r="V66" s="53" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="121" t="n"/>
+      <c r="B67" s="121" t="inlineStr">
         <is>
           <t>★固定資産関連費（減価償却費、固定資産税、保険料）の月々の金額は、＜経費＞の欄に記載をしてください。こちらの設備投資は、購入金額、どのような資産を何台購入するかです。</t>
         </is>
       </c>
-      <c r="C66" s="121" t="n"/>
-      <c r="D66" s="121" t="n"/>
-      <c r="E66" s="121" t="n"/>
-      <c r="F66" s="121" t="n"/>
-      <c r="G66" s="121" t="n"/>
-      <c r="H66" s="121" t="n"/>
-      <c r="I66" s="121" t="n"/>
-      <c r="J66" s="121" t="n"/>
+      <c r="C67" s="121" t="n"/>
+      <c r="D67" s="121" t="n"/>
+      <c r="E67" s="121" t="n"/>
+      <c r="F67" s="121" t="n"/>
+      <c r="G67" s="121" t="n"/>
+      <c r="H67" s="121" t="n"/>
+      <c r="I67" s="121" t="n"/>
+      <c r="J67" s="121" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="P1w1NeOlUabrDApEg3OQXA==" formatRows="1" sort="1" spinCount="100000" hashValue="1cGxtXL4c7J8cIANrYPk7nA6FqC/XiEANbxtfnwBv8/G+3xIbbA3dGIYhccwzKKVmCaLvR5TSgRQ6sGUwasjMg=="/>

--- a/Projects/rfa/drafts/プロジェクト情報申請書_FY26_RFA_事業計画.xlsx
+++ b/Projects/rfa/drafts/プロジェクト情報申請書_FY26_RFA_事業計画.xlsx
@@ -4405,7 +4405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X67"/>
+  <dimension ref="A1:X66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.625" defaultRowHeight="15.75"/>
   <cols>
     <col width="8.625" customWidth="1" style="18" min="1" max="1"/>
@@ -6491,398 +6491,392 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t>（追加④）PoC現場対応</t>
-        </is>
-      </c>
-      <c r="D41" s="0">
+      <c r="B41" s="125" t="inlineStr">
+        <is>
+          <t>工数合計</t>
+        </is>
+      </c>
+      <c r="C41" s="165" t="n"/>
+      <c r="D41" s="102">
         <f>SUM(E41:P41)</f>
         <v/>
       </c>
-      <c r="E41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" s="0" t="n">
-        <v>1</v>
+      <c r="E41" s="90">
+        <f>SUM(E31:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="90">
+        <f>SUM(F31:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="90">
+        <f>SUM(G31:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="90">
+        <f>SUM(H31:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="90">
+        <f>SUM(I31:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="90">
+        <f>SUM(J31:J40)</f>
+        <v/>
+      </c>
+      <c r="K41" s="90">
+        <f>SUM(K31:K40)</f>
+        <v/>
+      </c>
+      <c r="L41" s="90">
+        <f>SUM(L31:L40)</f>
+        <v/>
+      </c>
+      <c r="M41" s="90">
+        <f>SUM(M31:M40)</f>
+        <v/>
+      </c>
+      <c r="N41" s="90">
+        <f>SUM(N31:N40)</f>
+        <v/>
+      </c>
+      <c r="O41" s="90">
+        <f>SUM(O31:O40)</f>
+        <v/>
+      </c>
+      <c r="P41" s="90">
+        <f>SUM(P31:P40)</f>
+        <v/>
+      </c>
+      <c r="Q41" s="24" t="n"/>
+      <c r="R41" s="89">
+        <f>SUM(E41:G41)</f>
+        <v/>
+      </c>
+      <c r="S41" s="89">
+        <f>SUM(H41:J41)</f>
+        <v/>
+      </c>
+      <c r="T41" s="89">
+        <f>SUM(K41:M41)</f>
+        <v/>
+      </c>
+      <c r="U41" s="89">
+        <f>SUM(N41:P41)</f>
+        <v/>
+      </c>
+      <c r="V41" s="90">
+        <f>SUM(R41:U41)</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="125" t="inlineStr">
         <is>
-          <t>工数合計</t>
+          <t>金額合計（原価レート106万円）</t>
         </is>
       </c>
       <c r="C42" s="165" t="n"/>
-      <c r="D42" s="102">
-        <f>SUM(D31:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="90">
-        <f>SUM(E31:E41)</f>
-        <v/>
-      </c>
-      <c r="F42" s="90">
-        <f>SUM(F31:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="90">
-        <f>SUM(G31:G41)</f>
-        <v/>
-      </c>
-      <c r="H42" s="90">
-        <f>SUM(H31:H41)</f>
-        <v/>
-      </c>
-      <c r="I42" s="90">
-        <f>SUM(I31:I41)</f>
-        <v/>
-      </c>
-      <c r="J42" s="90">
-        <f>SUM(J31:J41)</f>
-        <v/>
-      </c>
-      <c r="K42" s="90">
-        <f>SUM(K31:K41)</f>
-        <v/>
-      </c>
-      <c r="L42" s="90">
-        <f>SUM(L31:L41)</f>
-        <v/>
-      </c>
-      <c r="M42" s="90">
-        <f>SUM(M31:M41)</f>
-        <v/>
-      </c>
-      <c r="N42" s="90">
-        <f>SUM(N31:N41)</f>
-        <v/>
-      </c>
-      <c r="O42" s="90">
-        <f>SUM(O31:O41)</f>
-        <v/>
-      </c>
-      <c r="P42" s="90">
-        <f>SUM(P31:P41)</f>
-        <v/>
-      </c>
-      <c r="Q42" s="24" t="n"/>
-      <c r="R42" s="89">
-        <f>SUM(E41:G41)</f>
-        <v/>
-      </c>
-      <c r="S42" s="89">
-        <f>SUM(H41:J41)</f>
-        <v/>
-      </c>
-      <c r="T42" s="89">
-        <f>SUM(K41:M41)</f>
-        <v/>
-      </c>
-      <c r="U42" s="89">
-        <f>SUM(N41:P41)</f>
-        <v/>
-      </c>
-      <c r="V42" s="90">
-        <f>SUM(R41:U41)</f>
+      <c r="D42" s="88">
+        <f>D41*1060000</f>
+        <v/>
+      </c>
+      <c r="E42" s="88">
+        <f>E41*1060000</f>
+        <v/>
+      </c>
+      <c r="F42" s="88">
+        <f>F41*1060000</f>
+        <v/>
+      </c>
+      <c r="G42" s="88">
+        <f>G41*1060000</f>
+        <v/>
+      </c>
+      <c r="H42" s="88">
+        <f>H41*1060000</f>
+        <v/>
+      </c>
+      <c r="I42" s="88">
+        <f>I41*1060000</f>
+        <v/>
+      </c>
+      <c r="J42" s="88">
+        <f>J41*1060000</f>
+        <v/>
+      </c>
+      <c r="K42" s="88">
+        <f>K41*1060000</f>
+        <v/>
+      </c>
+      <c r="L42" s="88">
+        <f>L41*1060000</f>
+        <v/>
+      </c>
+      <c r="M42" s="88">
+        <f>M41*1060000</f>
+        <v/>
+      </c>
+      <c r="N42" s="88">
+        <f>N41*1060000</f>
+        <v/>
+      </c>
+      <c r="O42" s="88">
+        <f>O41*1060000</f>
+        <v/>
+      </c>
+      <c r="P42" s="88">
+        <f>P41*1060000</f>
+        <v/>
+      </c>
+      <c r="Q42" s="18" t="n"/>
+      <c r="R42" s="88">
+        <f>R41*1060000</f>
+        <v/>
+      </c>
+      <c r="S42" s="88">
+        <f>S41*1060000</f>
+        <v/>
+      </c>
+      <c r="T42" s="88">
+        <f>T41*1060000</f>
+        <v/>
+      </c>
+      <c r="U42" s="88">
+        <f>U41*1060000</f>
+        <v/>
+      </c>
+      <c r="V42" s="88">
+        <f>SUM(R42:U42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="125" t="inlineStr">
-        <is>
-          <t>金額合計（原価レート106万円）</t>
-        </is>
-      </c>
-      <c r="C43" s="165" t="n"/>
-      <c r="D43" s="88">
-        <f>D42*1060000</f>
-        <v/>
-      </c>
-      <c r="E43" s="88">
-        <f>E42*1060000</f>
-        <v/>
-      </c>
-      <c r="F43" s="88">
-        <f>F42*1060000</f>
-        <v/>
-      </c>
-      <c r="G43" s="88">
-        <f>G42*1060000</f>
-        <v/>
-      </c>
-      <c r="H43" s="88">
-        <f>H42*1060000</f>
-        <v/>
-      </c>
-      <c r="I43" s="88">
-        <f>I42*1060000</f>
-        <v/>
-      </c>
-      <c r="J43" s="88">
-        <f>J42*1060000</f>
-        <v/>
-      </c>
-      <c r="K43" s="88">
-        <f>K42*1060000</f>
-        <v/>
-      </c>
-      <c r="L43" s="88">
-        <f>L42*1060000</f>
-        <v/>
-      </c>
-      <c r="M43" s="88">
-        <f>M42*1060000</f>
-        <v/>
-      </c>
-      <c r="N43" s="88">
-        <f>N42*1060000</f>
-        <v/>
-      </c>
-      <c r="O43" s="88">
-        <f>O42*1060000</f>
-        <v/>
-      </c>
-      <c r="P43" s="88">
-        <f>P42*1060000</f>
-        <v/>
-      </c>
       <c r="Q43" s="18" t="n"/>
-      <c r="R43" s="88">
-        <f>R41*1060000</f>
-        <v/>
-      </c>
-      <c r="S43" s="88">
-        <f>S41*1060000</f>
-        <v/>
-      </c>
-      <c r="T43" s="88">
-        <f>T41*1060000</f>
-        <v/>
-      </c>
-      <c r="U43" s="88">
-        <f>U41*1060000</f>
-        <v/>
-      </c>
-      <c r="V43" s="88">
-        <f>SUM(R42:U42)</f>
-        <v/>
-      </c>
     </row>
     <row r="44">
-      <c r="Q44" s="18" t="n"/>
+      <c r="B44" s="111" t="inlineStr">
+        <is>
+          <t>CEC費用負担分</t>
+        </is>
+      </c>
+      <c r="C44" s="112" t="n"/>
+      <c r="D44" s="127" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="E44" s="128" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="F44" s="128" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="G44" s="128" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="H44" s="128" t="inlineStr">
+        <is>
+          <t>７月</t>
+        </is>
+      </c>
+      <c r="I44" s="128" t="inlineStr">
+        <is>
+          <t>８月</t>
+        </is>
+      </c>
+      <c r="J44" s="128" t="inlineStr">
+        <is>
+          <t>９月</t>
+        </is>
+      </c>
+      <c r="K44" s="128" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="L44" s="128" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="M44" s="128" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="N44" s="128" t="inlineStr">
+        <is>
+          <t>１月</t>
+        </is>
+      </c>
+      <c r="O44" s="128" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="P44" s="129" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="Q44" s="19" t="n"/>
+      <c r="R44" s="129" t="inlineStr">
+        <is>
+          <t>１Q計画</t>
+        </is>
+      </c>
+      <c r="S44" s="130" t="inlineStr">
+        <is>
+          <t>２Q計画</t>
+        </is>
+      </c>
+      <c r="T44" s="130" t="inlineStr">
+        <is>
+          <t>３Q計画</t>
+        </is>
+      </c>
+      <c r="U44" s="130" t="inlineStr">
+        <is>
+          <t>4Q計画</t>
+        </is>
+      </c>
+      <c r="V44" s="130" t="inlineStr">
+        <is>
+          <t>合計計画</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="29.1" customHeight="1" s="154">
-      <c r="B45" s="111" t="inlineStr">
-        <is>
-          <t>CEC費用負担分</t>
-        </is>
-      </c>
-      <c r="C45" s="112" t="n"/>
-      <c r="D45" s="127" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="E45" s="128" t="inlineStr">
-        <is>
-          <t>4月</t>
-        </is>
-      </c>
-      <c r="F45" s="128" t="inlineStr">
-        <is>
-          <t>5月</t>
-        </is>
-      </c>
-      <c r="G45" s="128" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="H45" s="128" t="inlineStr">
-        <is>
-          <t>７月</t>
-        </is>
-      </c>
-      <c r="I45" s="128" t="inlineStr">
-        <is>
-          <t>８月</t>
-        </is>
-      </c>
-      <c r="J45" s="128" t="inlineStr">
-        <is>
-          <t>９月</t>
-        </is>
-      </c>
-      <c r="K45" s="128" t="inlineStr">
-        <is>
-          <t>10月</t>
-        </is>
-      </c>
-      <c r="L45" s="128" t="inlineStr">
-        <is>
-          <t>11月</t>
-        </is>
-      </c>
-      <c r="M45" s="128" t="inlineStr">
-        <is>
-          <t>12月</t>
-        </is>
-      </c>
-      <c r="N45" s="128" t="inlineStr">
-        <is>
-          <t>１月</t>
-        </is>
-      </c>
-      <c r="O45" s="128" t="inlineStr">
-        <is>
-          <t>2月</t>
-        </is>
-      </c>
-      <c r="P45" s="129" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
-      <c r="Q45" s="19" t="n"/>
-      <c r="R45" s="129" t="inlineStr">
-        <is>
-          <t>１Q計画</t>
-        </is>
-      </c>
-      <c r="S45" s="130" t="inlineStr">
-        <is>
-          <t>２Q計画</t>
-        </is>
-      </c>
-      <c r="T45" s="130" t="inlineStr">
-        <is>
-          <t>３Q計画</t>
-        </is>
-      </c>
-      <c r="U45" s="130" t="inlineStr">
-        <is>
-          <t>4Q計画</t>
-        </is>
-      </c>
-      <c r="V45" s="130" t="inlineStr">
-        <is>
-          <t>合計計画</t>
-        </is>
+      <c r="B45" s="113" t="inlineStr">
+        <is>
+          <t>＜経費＞</t>
+        </is>
+      </c>
+      <c r="C45" s="93" t="inlineStr">
+        <is>
+          <t>明細</t>
+        </is>
+      </c>
+      <c r="D45" s="100">
+        <f>SUM(E45:P45)</f>
+        <v/>
+      </c>
+      <c r="E45" s="93">
+        <f>SUM(E46:E49)</f>
+        <v/>
+      </c>
+      <c r="F45" s="93">
+        <f>SUM(F46:F49)</f>
+        <v/>
+      </c>
+      <c r="G45" s="93">
+        <f>SUM(G46:G49)</f>
+        <v/>
+      </c>
+      <c r="H45" s="93">
+        <f>SUM(H46:H49)</f>
+        <v/>
+      </c>
+      <c r="I45" s="93">
+        <f>SUM(I46:I49)</f>
+        <v/>
+      </c>
+      <c r="J45" s="93">
+        <f>SUM(J46:J49)</f>
+        <v/>
+      </c>
+      <c r="K45" s="93">
+        <f>SUM(K46:K49)</f>
+        <v/>
+      </c>
+      <c r="L45" s="93">
+        <f>SUM(L46:L49)</f>
+        <v/>
+      </c>
+      <c r="M45" s="93">
+        <f>SUM(M46:M49)</f>
+        <v/>
+      </c>
+      <c r="N45" s="93">
+        <f>SUM(N46:N49)</f>
+        <v/>
+      </c>
+      <c r="O45" s="93">
+        <f>SUM(O46:O49)</f>
+        <v/>
+      </c>
+      <c r="P45" s="93">
+        <f>SUM(P46:P49)</f>
+        <v/>
+      </c>
+      <c r="Q45" s="18" t="n"/>
+      <c r="R45" s="93">
+        <f>SUM(E45:G45)</f>
+        <v/>
+      </c>
+      <c r="S45" s="94">
+        <f>SUM(H45:J45)</f>
+        <v/>
+      </c>
+      <c r="T45" s="93">
+        <f>SUM(K45:M45)</f>
+        <v/>
+      </c>
+      <c r="U45" s="93">
+        <f>SUM(N45:P45)</f>
+        <v/>
+      </c>
+      <c r="V45" s="93">
+        <f>SUM(R45:U45)</f>
+        <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="113" t="inlineStr">
-        <is>
-          <t>＜経費＞</t>
-        </is>
-      </c>
-      <c r="C46" s="93" t="inlineStr">
-        <is>
-          <t>明細</t>
-        </is>
-      </c>
-      <c r="D46" s="100">
-        <f>SUM(E45:P45)</f>
-        <v/>
-      </c>
-      <c r="E46" s="93">
-        <f>SUM(E46:E49)</f>
-        <v/>
-      </c>
-      <c r="F46" s="93">
-        <f>SUM(F46:F49)</f>
-        <v/>
-      </c>
-      <c r="G46" s="93">
-        <f>SUM(G46:G49)</f>
-        <v/>
-      </c>
-      <c r="H46" s="93">
-        <f>SUM(H46:H49)</f>
-        <v/>
-      </c>
-      <c r="I46" s="93">
-        <f>SUM(I46:I49)</f>
-        <v/>
-      </c>
-      <c r="J46" s="93">
-        <f>SUM(J46:J49)</f>
-        <v/>
-      </c>
-      <c r="K46" s="93">
-        <f>SUM(K46:K49)</f>
-        <v/>
-      </c>
-      <c r="L46" s="93">
-        <f>SUM(L46:L49)</f>
-        <v/>
-      </c>
-      <c r="M46" s="93">
-        <f>SUM(M46:M49)</f>
-        <v/>
-      </c>
-      <c r="N46" s="93">
-        <f>SUM(N46:N49)</f>
-        <v/>
-      </c>
-      <c r="O46" s="93">
-        <f>SUM(O46:O49)</f>
-        <v/>
-      </c>
-      <c r="P46" s="93">
-        <f>SUM(P46:P49)</f>
-        <v/>
-      </c>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="39" t="n"/>
+      <c r="D46" s="93">
+        <f>SUM(E46:P46)</f>
+        <v/>
+      </c>
+      <c r="E46" s="39" t="n"/>
+      <c r="F46" s="39" t="n"/>
+      <c r="G46" s="39" t="n"/>
+      <c r="H46" s="39" t="n"/>
+      <c r="I46" s="39" t="n"/>
+      <c r="J46" s="39" t="n"/>
+      <c r="K46" s="39" t="n"/>
+      <c r="L46" s="39" t="n"/>
+      <c r="M46" s="39" t="n"/>
+      <c r="N46" s="39" t="n"/>
+      <c r="O46" s="39" t="n"/>
+      <c r="P46" s="39" t="n"/>
       <c r="Q46" s="18" t="n"/>
       <c r="R46" s="93">
-        <f>SUM(E45:G45)</f>
+        <f>SUM(E46:G46)</f>
         <v/>
       </c>
       <c r="S46" s="94">
-        <f>SUM(H45:J45)</f>
+        <f>SUM(H46:J46)</f>
         <v/>
       </c>
       <c r="T46" s="93">
-        <f>SUM(K45:M45)</f>
+        <f>SUM(K46:M46)</f>
         <v/>
       </c>
       <c r="U46" s="93">
-        <f>SUM(N45:P45)</f>
+        <f>SUM(N46:P46)</f>
         <v/>
       </c>
       <c r="V46" s="93">
-        <f>SUM(R45:U45)</f>
+        <f>SUM(R46:U46)</f>
         <v/>
       </c>
     </row>
@@ -6890,7 +6884,7 @@
       <c r="B47" s="20" t="n"/>
       <c r="C47" s="39" t="n"/>
       <c r="D47" s="93">
-        <f>SUM(E46:P46)</f>
+        <f>SUM(E47:P47)</f>
         <v/>
       </c>
       <c r="E47" s="39" t="n"/>
@@ -6907,23 +6901,23 @@
       <c r="P47" s="39" t="n"/>
       <c r="Q47" s="18" t="n"/>
       <c r="R47" s="93">
-        <f>SUM(E46:G46)</f>
+        <f>SUM(E47:G47)</f>
         <v/>
       </c>
       <c r="S47" s="94">
-        <f>SUM(H46:J46)</f>
+        <f>SUM(H47:J47)</f>
         <v/>
       </c>
       <c r="T47" s="93">
-        <f>SUM(K46:M46)</f>
+        <f>SUM(K47:M47)</f>
         <v/>
       </c>
       <c r="U47" s="93">
-        <f>SUM(N46:P46)</f>
+        <f>SUM(N47:P47)</f>
         <v/>
       </c>
       <c r="V47" s="93">
-        <f>SUM(R46:U46)</f>
+        <f>SUM(R47:U47)</f>
         <v/>
       </c>
     </row>
@@ -6931,7 +6925,7 @@
       <c r="B48" s="20" t="n"/>
       <c r="C48" s="39" t="n"/>
       <c r="D48" s="93">
-        <f>SUM(E47:P47)</f>
+        <f>SUM(E48:P48)</f>
         <v/>
       </c>
       <c r="E48" s="39" t="n"/>
@@ -6948,23 +6942,23 @@
       <c r="P48" s="39" t="n"/>
       <c r="Q48" s="18" t="n"/>
       <c r="R48" s="93">
-        <f>SUM(E47:G47)</f>
+        <f>SUM(E48:G48)</f>
         <v/>
       </c>
       <c r="S48" s="94">
-        <f>SUM(H47:J47)</f>
+        <f>SUM(H48:J48)</f>
         <v/>
       </c>
       <c r="T48" s="93">
-        <f>SUM(K47:M47)</f>
+        <f>SUM(K48:M48)</f>
         <v/>
       </c>
       <c r="U48" s="93">
-        <f>SUM(N47:P47)</f>
+        <f>SUM(N48:P48)</f>
         <v/>
       </c>
       <c r="V48" s="93">
-        <f>SUM(R47:U47)</f>
+        <f>SUM(R48:U48)</f>
         <v/>
       </c>
     </row>
@@ -6972,7 +6966,7 @@
       <c r="B49" s="20" t="n"/>
       <c r="C49" s="39" t="n"/>
       <c r="D49" s="93">
-        <f>SUM(E48:P48)</f>
+        <f>SUM(E49:P49)</f>
         <v/>
       </c>
       <c r="E49" s="39" t="n"/>
@@ -6989,265 +6983,265 @@
       <c r="P49" s="39" t="n"/>
       <c r="Q49" s="18" t="n"/>
       <c r="R49" s="93">
-        <f>SUM(E48:G48)</f>
+        <f>SUM(E49:G49)</f>
         <v/>
       </c>
       <c r="S49" s="94">
-        <f>SUM(H48:J48)</f>
+        <f>SUM(H49:J49)</f>
         <v/>
       </c>
       <c r="T49" s="93">
-        <f>SUM(K48:M48)</f>
+        <f>SUM(K49:M49)</f>
         <v/>
       </c>
       <c r="U49" s="93">
-        <f>SUM(N48:P48)</f>
+        <f>SUM(N49:P49)</f>
         <v/>
       </c>
       <c r="V49" s="93">
-        <f>SUM(R48:U48)</f>
+        <f>SUM(R49:U49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="20" t="n"/>
-      <c r="C50" s="39" t="n"/>
-      <c r="D50" s="93">
-        <f>SUM(E49:P49)</f>
-        <v/>
-      </c>
-      <c r="E50" s="39" t="n"/>
-      <c r="F50" s="39" t="n"/>
-      <c r="G50" s="39" t="n"/>
-      <c r="H50" s="39" t="n"/>
-      <c r="I50" s="39" t="n"/>
-      <c r="J50" s="39" t="n"/>
-      <c r="K50" s="39" t="n"/>
-      <c r="L50" s="39" t="n"/>
-      <c r="M50" s="39" t="n"/>
-      <c r="N50" s="39" t="n"/>
-      <c r="O50" s="39" t="n"/>
-      <c r="P50" s="39" t="n"/>
+      <c r="D50" s="47" t="n"/>
       <c r="Q50" s="18" t="n"/>
-      <c r="R50" s="93">
-        <f>SUM(E49:G49)</f>
-        <v/>
-      </c>
-      <c r="S50" s="94">
-        <f>SUM(H49:J49)</f>
-        <v/>
-      </c>
-      <c r="T50" s="93">
-        <f>SUM(K49:M49)</f>
-        <v/>
-      </c>
-      <c r="U50" s="93">
-        <f>SUM(N49:P49)</f>
-        <v/>
-      </c>
-      <c r="V50" s="93">
-        <f>SUM(R49:U49)</f>
-        <v/>
-      </c>
+      <c r="R50" s="46" t="n"/>
     </row>
     <row r="51">
-      <c r="D51" s="47" t="n"/>
-      <c r="Q51" s="18" t="n"/>
-      <c r="R51" s="46" t="n"/>
+      <c r="B51" s="111" t="inlineStr">
+        <is>
+          <t>海外研人件費　＊個別委託契約は、経費の研究費計上</t>
+        </is>
+      </c>
+      <c r="C51" s="112" t="n"/>
+      <c r="D51" s="127" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="E51" s="128" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="F51" s="128" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="G51" s="128" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="H51" s="128" t="inlineStr">
+        <is>
+          <t>７月</t>
+        </is>
+      </c>
+      <c r="I51" s="128" t="inlineStr">
+        <is>
+          <t>８月</t>
+        </is>
+      </c>
+      <c r="J51" s="128" t="inlineStr">
+        <is>
+          <t>９月</t>
+        </is>
+      </c>
+      <c r="K51" s="128" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="L51" s="128" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="M51" s="128" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="N51" s="128" t="inlineStr">
+        <is>
+          <t>１月</t>
+        </is>
+      </c>
+      <c r="O51" s="128" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="P51" s="129" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="Q51" s="19" t="n"/>
+      <c r="R51" s="129" t="inlineStr">
+        <is>
+          <t>１Q計画</t>
+        </is>
+      </c>
+      <c r="S51" s="130" t="inlineStr">
+        <is>
+          <t>２Q計画</t>
+        </is>
+      </c>
+      <c r="T51" s="130" t="inlineStr">
+        <is>
+          <t>３Q計画</t>
+        </is>
+      </c>
+      <c r="U51" s="130" t="inlineStr">
+        <is>
+          <t>4Q計画</t>
+        </is>
+      </c>
+      <c r="V51" s="130" t="inlineStr">
+        <is>
+          <t>合計計画</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="29.1" customHeight="1" s="154">
-      <c r="B52" s="111" t="inlineStr">
-        <is>
-          <t>海外研人件費　＊個別委託契約は、経費の研究費計上</t>
-        </is>
-      </c>
-      <c r="C52" s="112" t="n"/>
-      <c r="D52" s="127" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="E52" s="128" t="inlineStr">
-        <is>
-          <t>4月</t>
-        </is>
-      </c>
-      <c r="F52" s="128" t="inlineStr">
-        <is>
-          <t>5月</t>
-        </is>
-      </c>
-      <c r="G52" s="128" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="H52" s="128" t="inlineStr">
-        <is>
-          <t>７月</t>
-        </is>
-      </c>
-      <c r="I52" s="128" t="inlineStr">
-        <is>
-          <t>８月</t>
-        </is>
-      </c>
-      <c r="J52" s="128" t="inlineStr">
-        <is>
-          <t>９月</t>
-        </is>
-      </c>
-      <c r="K52" s="128" t="inlineStr">
-        <is>
-          <t>10月</t>
-        </is>
-      </c>
-      <c r="L52" s="128" t="inlineStr">
-        <is>
-          <t>11月</t>
-        </is>
-      </c>
-      <c r="M52" s="128" t="inlineStr">
-        <is>
-          <t>12月</t>
-        </is>
-      </c>
-      <c r="N52" s="128" t="inlineStr">
-        <is>
-          <t>１月</t>
-        </is>
-      </c>
-      <c r="O52" s="128" t="inlineStr">
-        <is>
-          <t>2月</t>
-        </is>
-      </c>
-      <c r="P52" s="129" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
-      <c r="Q52" s="19" t="n"/>
-      <c r="R52" s="129" t="inlineStr">
-        <is>
-          <t>１Q計画</t>
-        </is>
-      </c>
-      <c r="S52" s="130" t="inlineStr">
-        <is>
-          <t>２Q計画</t>
-        </is>
-      </c>
-      <c r="T52" s="130" t="inlineStr">
-        <is>
-          <t>３Q計画</t>
-        </is>
-      </c>
-      <c r="U52" s="130" t="inlineStr">
-        <is>
-          <t>4Q計画</t>
-        </is>
-      </c>
-      <c r="V52" s="130" t="inlineStr">
-        <is>
-          <t>合計計画</t>
-        </is>
+      <c r="B52" s="113" t="inlineStr">
+        <is>
+          <t>＜経費＞</t>
+        </is>
+      </c>
+      <c r="C52" s="93" t="inlineStr">
+        <is>
+          <t>明細</t>
+        </is>
+      </c>
+      <c r="D52" s="100">
+        <f>SUM(E52:P52)</f>
+        <v/>
+      </c>
+      <c r="E52" s="93">
+        <f>SUM(E53:E56)</f>
+        <v/>
+      </c>
+      <c r="F52" s="93">
+        <f>SUM(F53:F56)</f>
+        <v/>
+      </c>
+      <c r="G52" s="93">
+        <f>SUM(G53:G56)</f>
+        <v/>
+      </c>
+      <c r="H52" s="93">
+        <f>SUM(H53:H56)</f>
+        <v/>
+      </c>
+      <c r="I52" s="93">
+        <f>SUM(I53:I56)</f>
+        <v/>
+      </c>
+      <c r="J52" s="93">
+        <f>SUM(J53:J56)</f>
+        <v/>
+      </c>
+      <c r="K52" s="93">
+        <f>SUM(K53:K56)</f>
+        <v/>
+      </c>
+      <c r="L52" s="93">
+        <f>SUM(L53:L56)</f>
+        <v/>
+      </c>
+      <c r="M52" s="93">
+        <f>SUM(M53:M56)</f>
+        <v/>
+      </c>
+      <c r="N52" s="93">
+        <f>SUM(N53:N56)</f>
+        <v/>
+      </c>
+      <c r="O52" s="93">
+        <f>SUM(O53:O56)</f>
+        <v/>
+      </c>
+      <c r="P52" s="93">
+        <f>SUM(P53:P56)</f>
+        <v/>
+      </c>
+      <c r="Q52" s="18" t="n"/>
+      <c r="R52" s="93">
+        <f>SUM(E52:G52)</f>
+        <v/>
+      </c>
+      <c r="S52" s="94">
+        <f>SUM(H52:J52)</f>
+        <v/>
+      </c>
+      <c r="T52" s="93">
+        <f>SUM(K52:M52)</f>
+        <v/>
+      </c>
+      <c r="U52" s="93">
+        <f>SUM(N52:P52)</f>
+        <v/>
+      </c>
+      <c r="V52" s="93">
+        <f>SUM(R52:U52)</f>
+        <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="113" t="inlineStr">
-        <is>
-          <t>＜経費＞</t>
-        </is>
-      </c>
-      <c r="C53" s="93" t="inlineStr">
-        <is>
-          <t>明細</t>
-        </is>
-      </c>
-      <c r="D53" s="100">
-        <f>SUM(E52:P52)</f>
-        <v/>
-      </c>
-      <c r="E53" s="93">
-        <f>SUM(E53:E56)</f>
-        <v/>
-      </c>
-      <c r="F53" s="93">
-        <f>SUM(F53:F56)</f>
-        <v/>
-      </c>
-      <c r="G53" s="93">
-        <f>SUM(G53:G56)</f>
-        <v/>
-      </c>
-      <c r="H53" s="93">
-        <f>SUM(H53:H56)</f>
-        <v/>
-      </c>
-      <c r="I53" s="93">
-        <f>SUM(I53:I56)</f>
-        <v/>
-      </c>
-      <c r="J53" s="93">
-        <f>SUM(J53:J56)</f>
-        <v/>
-      </c>
-      <c r="K53" s="93">
-        <f>SUM(K53:K56)</f>
-        <v/>
-      </c>
-      <c r="L53" s="93">
-        <f>SUM(L53:L56)</f>
-        <v/>
-      </c>
-      <c r="M53" s="93">
-        <f>SUM(M53:M56)</f>
-        <v/>
-      </c>
-      <c r="N53" s="93">
-        <f>SUM(N53:N56)</f>
-        <v/>
-      </c>
-      <c r="O53" s="93">
-        <f>SUM(O53:O56)</f>
-        <v/>
-      </c>
-      <c r="P53" s="93">
-        <f>SUM(P53:P56)</f>
-        <v/>
-      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>研究費</t>
+        </is>
+      </c>
+      <c r="C53" s="39" t="n"/>
+      <c r="D53" s="93">
+        <f>SUM(E53:P53)</f>
+        <v/>
+      </c>
+      <c r="E53" s="39" t="n"/>
+      <c r="F53" s="39" t="n"/>
+      <c r="G53" s="39" t="n"/>
+      <c r="H53" s="39" t="n"/>
+      <c r="I53" s="39" t="n"/>
+      <c r="J53" s="39" t="n"/>
+      <c r="K53" s="39" t="n"/>
+      <c r="L53" s="39" t="n"/>
+      <c r="M53" s="39" t="n"/>
+      <c r="N53" s="39" t="n"/>
+      <c r="O53" s="39" t="n"/>
+      <c r="P53" s="39" t="n"/>
       <c r="Q53" s="18" t="n"/>
       <c r="R53" s="93">
-        <f>SUM(E52:G52)</f>
+        <f>SUM(E53:G53)</f>
         <v/>
       </c>
       <c r="S53" s="94">
-        <f>SUM(H52:J52)</f>
+        <f>SUM(H53:J53)</f>
         <v/>
       </c>
       <c r="T53" s="93">
-        <f>SUM(K52:M52)</f>
+        <f>SUM(K53:M53)</f>
         <v/>
       </c>
       <c r="U53" s="93">
-        <f>SUM(N52:P52)</f>
+        <f>SUM(N53:P53)</f>
         <v/>
       </c>
       <c r="V53" s="93">
-        <f>SUM(R52:U52)</f>
+        <f>SUM(R53:U53)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="20" t="inlineStr">
-        <is>
-          <t>研究費</t>
-        </is>
-      </c>
+      <c r="B54" s="20" t="n"/>
       <c r="C54" s="39" t="n"/>
       <c r="D54" s="93">
-        <f>SUM(E53:P53)</f>
+        <f>SUM(E54:P54)</f>
         <v/>
       </c>
       <c r="E54" s="39" t="n"/>
@@ -7264,23 +7258,23 @@
       <c r="P54" s="39" t="n"/>
       <c r="Q54" s="18" t="n"/>
       <c r="R54" s="93">
-        <f>SUM(E53:G53)</f>
+        <f>SUM(E54:G54)</f>
         <v/>
       </c>
       <c r="S54" s="94">
-        <f>SUM(H53:J53)</f>
+        <f>SUM(H54:J54)</f>
         <v/>
       </c>
       <c r="T54" s="93">
-        <f>SUM(K53:M53)</f>
+        <f>SUM(K54:M54)</f>
         <v/>
       </c>
       <c r="U54" s="93">
-        <f>SUM(N53:P53)</f>
+        <f>SUM(N54:P54)</f>
         <v/>
       </c>
       <c r="V54" s="93">
-        <f>SUM(R53:U53)</f>
+        <f>SUM(R54:U54)</f>
         <v/>
       </c>
     </row>
@@ -7288,7 +7282,7 @@
       <c r="B55" s="20" t="n"/>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="93">
-        <f>SUM(E54:P54)</f>
+        <f>SUM(E55:P55)</f>
         <v/>
       </c>
       <c r="E55" s="39" t="n"/>
@@ -7305,23 +7299,23 @@
       <c r="P55" s="39" t="n"/>
       <c r="Q55" s="18" t="n"/>
       <c r="R55" s="93">
-        <f>SUM(E54:G54)</f>
+        <f>SUM(E55:G55)</f>
         <v/>
       </c>
       <c r="S55" s="94">
-        <f>SUM(H54:J54)</f>
+        <f>SUM(H55:J55)</f>
         <v/>
       </c>
       <c r="T55" s="93">
-        <f>SUM(K54:M54)</f>
+        <f>SUM(K55:M55)</f>
         <v/>
       </c>
       <c r="U55" s="93">
-        <f>SUM(N54:P54)</f>
+        <f>SUM(N55:P55)</f>
         <v/>
       </c>
       <c r="V55" s="93">
-        <f>SUM(R54:U54)</f>
+        <f>SUM(R55:U55)</f>
         <v/>
       </c>
     </row>
@@ -7329,7 +7323,7 @@
       <c r="B56" s="20" t="n"/>
       <c r="C56" s="39" t="n"/>
       <c r="D56" s="93">
-        <f>SUM(E55:P55)</f>
+        <f>SUM(E56:P56)</f>
         <v/>
       </c>
       <c r="E56" s="39" t="n"/>
@@ -7346,261 +7340,260 @@
       <c r="P56" s="39" t="n"/>
       <c r="Q56" s="18" t="n"/>
       <c r="R56" s="93">
-        <f>SUM(E55:G55)</f>
+        <f>SUM(E56:G56)</f>
         <v/>
       </c>
       <c r="S56" s="94">
-        <f>SUM(H55:J55)</f>
+        <f>SUM(H56:J56)</f>
         <v/>
       </c>
       <c r="T56" s="93">
-        <f>SUM(K55:M55)</f>
+        <f>SUM(K56:M56)</f>
         <v/>
       </c>
       <c r="U56" s="93">
-        <f>SUM(N55:P55)</f>
+        <f>SUM(N56:P56)</f>
         <v/>
       </c>
       <c r="V56" s="93">
-        <f>SUM(R55:U55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="20" t="n"/>
-      <c r="C57" s="39" t="n"/>
-      <c r="D57" s="93">
-        <f>SUM(E56:P56)</f>
-        <v/>
-      </c>
-      <c r="E57" s="39" t="n"/>
-      <c r="F57" s="39" t="n"/>
-      <c r="G57" s="39" t="n"/>
-      <c r="H57" s="39" t="n"/>
-      <c r="I57" s="39" t="n"/>
-      <c r="J57" s="39" t="n"/>
-      <c r="K57" s="39" t="n"/>
-      <c r="L57" s="39" t="n"/>
-      <c r="M57" s="39" t="n"/>
-      <c r="N57" s="39" t="n"/>
-      <c r="O57" s="39" t="n"/>
-      <c r="P57" s="39" t="n"/>
-      <c r="Q57" s="18" t="n"/>
-      <c r="R57" s="93">
-        <f>SUM(E56:G56)</f>
-        <v/>
-      </c>
-      <c r="S57" s="94">
-        <f>SUM(H56:J56)</f>
-        <v/>
-      </c>
-      <c r="T57" s="93">
-        <f>SUM(K56:M56)</f>
-        <v/>
-      </c>
-      <c r="U57" s="93">
-        <f>SUM(N56:P56)</f>
-        <v/>
-      </c>
-      <c r="V57" s="93">
         <f>SUM(R56:U56)</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1" s="154"/>
+    <row r="58" ht="30" customHeight="1" s="154">
+      <c r="B58" s="166" t="inlineStr">
+        <is>
+          <t>設備投資（固定資産購入を検討している場合は、購入金額をこちらに記載）</t>
+        </is>
+      </c>
+      <c r="C58" s="165" t="n"/>
+      <c r="D58" s="131" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="E58" s="132" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="F58" s="132" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="G58" s="132" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="H58" s="132" t="inlineStr">
+        <is>
+          <t>７月</t>
+        </is>
+      </c>
+      <c r="I58" s="132" t="inlineStr">
+        <is>
+          <t>８月</t>
+        </is>
+      </c>
+      <c r="J58" s="132" t="inlineStr">
+        <is>
+          <t>９月</t>
+        </is>
+      </c>
+      <c r="K58" s="132" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="L58" s="132" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="M58" s="132" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="N58" s="132" t="inlineStr">
+        <is>
+          <t>１月</t>
+        </is>
+      </c>
+      <c r="O58" s="132" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="P58" s="132" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="Q58" s="19" t="n"/>
+      <c r="R58" s="132" t="inlineStr">
+        <is>
+          <t>１Q計画</t>
+        </is>
+      </c>
+      <c r="S58" s="134" t="inlineStr">
+        <is>
+          <t>２Q計画</t>
+        </is>
+      </c>
+      <c r="T58" s="132" t="inlineStr">
+        <is>
+          <t>３Q計画</t>
+        </is>
+      </c>
+      <c r="U58" s="132" t="inlineStr">
+        <is>
+          <t>4Q計画</t>
+        </is>
+      </c>
+      <c r="V58" s="132" t="inlineStr">
+        <is>
+          <t>合計計画</t>
+        </is>
+      </c>
+    </row>
     <row r="59">
-      <c r="B59" s="166" t="inlineStr">
-        <is>
-          <t>設備投資（固定資産購入を検討している場合は、購入金額をこちらに記載）</t>
-        </is>
-      </c>
-      <c r="C59" s="165" t="n"/>
-      <c r="D59" s="131" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="E59" s="132" t="inlineStr">
-        <is>
-          <t>4月</t>
-        </is>
-      </c>
-      <c r="F59" s="132" t="inlineStr">
-        <is>
-          <t>5月</t>
-        </is>
-      </c>
-      <c r="G59" s="132" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="H59" s="132" t="inlineStr">
-        <is>
-          <t>７月</t>
-        </is>
-      </c>
-      <c r="I59" s="132" t="inlineStr">
-        <is>
-          <t>８月</t>
-        </is>
-      </c>
-      <c r="J59" s="132" t="inlineStr">
-        <is>
-          <t>９月</t>
-        </is>
-      </c>
-      <c r="K59" s="132" t="inlineStr">
-        <is>
-          <t>10月</t>
-        </is>
-      </c>
-      <c r="L59" s="132" t="inlineStr">
-        <is>
-          <t>11月</t>
-        </is>
-      </c>
-      <c r="M59" s="132" t="inlineStr">
-        <is>
-          <t>12月</t>
-        </is>
-      </c>
-      <c r="N59" s="132" t="inlineStr">
-        <is>
-          <t>１月</t>
-        </is>
-      </c>
-      <c r="O59" s="132" t="inlineStr">
-        <is>
-          <t>2月</t>
-        </is>
-      </c>
-      <c r="P59" s="132" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
-      <c r="Q59" s="19" t="n"/>
-      <c r="R59" s="132" t="inlineStr">
-        <is>
-          <t>１Q計画</t>
-        </is>
-      </c>
-      <c r="S59" s="134" t="inlineStr">
-        <is>
-          <t>２Q計画</t>
-        </is>
-      </c>
-      <c r="T59" s="132" t="inlineStr">
-        <is>
-          <t>３Q計画</t>
-        </is>
-      </c>
-      <c r="U59" s="132" t="inlineStr">
-        <is>
-          <t>4Q計画</t>
-        </is>
-      </c>
-      <c r="V59" s="132" t="inlineStr">
-        <is>
-          <t>合計計画</t>
-        </is>
+      <c r="B59" s="133" t="inlineStr">
+        <is>
+          <t>＜経費＞</t>
+        </is>
+      </c>
+      <c r="C59" s="97" t="inlineStr">
+        <is>
+          <t>明細</t>
+        </is>
+      </c>
+      <c r="D59" s="99">
+        <f>SUM(E59:P59)</f>
+        <v/>
+      </c>
+      <c r="E59" s="97">
+        <f>SUM(E60:E64)</f>
+        <v/>
+      </c>
+      <c r="F59" s="97">
+        <f>SUM(F60:F64)</f>
+        <v/>
+      </c>
+      <c r="G59" s="97">
+        <f>SUM(G60:G64)</f>
+        <v/>
+      </c>
+      <c r="H59" s="97">
+        <f>SUM(H60:H64)</f>
+        <v/>
+      </c>
+      <c r="I59" s="97">
+        <f>SUM(I60:I64)</f>
+        <v/>
+      </c>
+      <c r="J59" s="97">
+        <f>SUM(J60:J64)</f>
+        <v/>
+      </c>
+      <c r="K59" s="97">
+        <f>SUM(K60:K64)</f>
+        <v/>
+      </c>
+      <c r="L59" s="97">
+        <f>SUM(L60:L64)</f>
+        <v/>
+      </c>
+      <c r="M59" s="97">
+        <f>SUM(M60:M64)</f>
+        <v/>
+      </c>
+      <c r="N59" s="97">
+        <f>SUM(N60:N64)</f>
+        <v/>
+      </c>
+      <c r="O59" s="97">
+        <f>SUM(O60:O64)</f>
+        <v/>
+      </c>
+      <c r="P59" s="97">
+        <f>SUM(P60:P64)</f>
+        <v/>
+      </c>
+      <c r="Q59" s="18" t="n"/>
+      <c r="R59" s="97">
+        <f>SUM(E59:G59)</f>
+        <v/>
+      </c>
+      <c r="S59" s="98">
+        <f>SUM(H59:J59)</f>
+        <v/>
+      </c>
+      <c r="T59" s="97">
+        <f>SUM(K59:M59)</f>
+        <v/>
+      </c>
+      <c r="U59" s="97">
+        <f>SUM(N59:P59)</f>
+        <v/>
+      </c>
+      <c r="V59" s="97">
+        <f>SUM(R59:U59)</f>
+        <v/>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="133" t="inlineStr">
-        <is>
-          <t>＜経費＞</t>
-        </is>
-      </c>
-      <c r="C60" s="97" t="inlineStr">
-        <is>
-          <t>明細</t>
-        </is>
-      </c>
-      <c r="D60" s="99">
-        <f>SUM(E59:P59)</f>
-        <v/>
-      </c>
-      <c r="E60" s="97">
-        <f>SUM(E60:E64)</f>
-        <v/>
-      </c>
-      <c r="F60" s="97">
-        <f>SUM(F60:F64)</f>
-        <v/>
-      </c>
-      <c r="G60" s="97">
-        <f>SUM(G60:G64)</f>
-        <v/>
-      </c>
-      <c r="H60" s="97">
-        <f>SUM(H60:H64)</f>
-        <v/>
-      </c>
-      <c r="I60" s="97">
-        <f>SUM(I60:I64)</f>
-        <v/>
-      </c>
-      <c r="J60" s="97">
-        <f>SUM(J60:J64)</f>
-        <v/>
-      </c>
-      <c r="K60" s="97">
-        <f>SUM(K60:K64)</f>
-        <v/>
-      </c>
-      <c r="L60" s="97">
-        <f>SUM(L60:L64)</f>
-        <v/>
-      </c>
-      <c r="M60" s="97">
-        <f>SUM(M60:M64)</f>
-        <v/>
-      </c>
-      <c r="N60" s="97">
-        <f>SUM(N60:N64)</f>
-        <v/>
-      </c>
-      <c r="O60" s="97">
-        <f>SUM(O60:O64)</f>
-        <v/>
-      </c>
-      <c r="P60" s="97">
-        <f>SUM(P60:P64)</f>
-        <v/>
-      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>設備購入</t>
+        </is>
+      </c>
+      <c r="C60" s="39" t="n"/>
+      <c r="D60" s="97">
+        <f>SUM(E60:P60)</f>
+        <v/>
+      </c>
+      <c r="E60" s="39" t="n"/>
+      <c r="F60" s="39" t="n"/>
+      <c r="G60" s="39" t="n"/>
+      <c r="H60" s="39" t="n"/>
+      <c r="I60" s="39" t="n"/>
+      <c r="J60" s="39" t="n"/>
+      <c r="K60" s="39" t="n"/>
+      <c r="L60" s="39" t="n"/>
+      <c r="M60" s="39" t="n"/>
+      <c r="N60" s="39" t="n"/>
+      <c r="O60" s="39" t="n"/>
+      <c r="P60" s="39" t="n"/>
       <c r="Q60" s="18" t="n"/>
       <c r="R60" s="97">
-        <f>SUM(E59:G59)</f>
+        <f>SUM(E60:G60)</f>
         <v/>
       </c>
       <c r="S60" s="98">
-        <f>SUM(H59:J59)</f>
+        <f>SUM(H60:J60)</f>
         <v/>
       </c>
       <c r="T60" s="97">
-        <f>SUM(K59:M59)</f>
+        <f>SUM(K60:M60)</f>
         <v/>
       </c>
       <c r="U60" s="97">
-        <f>SUM(N59:P59)</f>
+        <f>SUM(N60:P60)</f>
         <v/>
       </c>
       <c r="V60" s="97">
-        <f>SUM(R59:U59)</f>
+        <f>SUM(R60:U60)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="20" t="inlineStr">
-        <is>
-          <t>設備購入</t>
-        </is>
-      </c>
+      <c r="B61" s="20" t="n"/>
       <c r="C61" s="39" t="n"/>
       <c r="D61" s="97">
-        <f>SUM(E60:P60)</f>
+        <f>SUM(E61:P61)</f>
         <v/>
       </c>
       <c r="E61" s="39" t="n"/>
@@ -7617,23 +7610,23 @@
       <c r="P61" s="39" t="n"/>
       <c r="Q61" s="18" t="n"/>
       <c r="R61" s="97">
-        <f>SUM(E60:G60)</f>
+        <f>SUM(E61:G61)</f>
         <v/>
       </c>
       <c r="S61" s="98">
-        <f>SUM(H60:J60)</f>
+        <f>SUM(H61:J61)</f>
         <v/>
       </c>
       <c r="T61" s="97">
-        <f>SUM(K60:M60)</f>
+        <f>SUM(K61:M61)</f>
         <v/>
       </c>
       <c r="U61" s="97">
-        <f>SUM(N60:P60)</f>
+        <f>SUM(N61:P61)</f>
         <v/>
       </c>
       <c r="V61" s="97">
-        <f>SUM(R60:U60)</f>
+        <f>SUM(R61:U61)</f>
         <v/>
       </c>
     </row>
@@ -7641,7 +7634,7 @@
       <c r="B62" s="20" t="n"/>
       <c r="C62" s="39" t="n"/>
       <c r="D62" s="97">
-        <f>SUM(E61:P61)</f>
+        <f>SUM(E62:P62)</f>
         <v/>
       </c>
       <c r="E62" s="39" t="n"/>
@@ -7658,23 +7651,23 @@
       <c r="P62" s="39" t="n"/>
       <c r="Q62" s="18" t="n"/>
       <c r="R62" s="97">
-        <f>SUM(E61:G61)</f>
+        <f>SUM(E62:G62)</f>
         <v/>
       </c>
       <c r="S62" s="98">
-        <f>SUM(H61:J61)</f>
+        <f>SUM(H62:J62)</f>
         <v/>
       </c>
       <c r="T62" s="97">
-        <f>SUM(K61:M61)</f>
+        <f>SUM(K62:M62)</f>
         <v/>
       </c>
       <c r="U62" s="97">
-        <f>SUM(N61:P61)</f>
+        <f>SUM(N62:P62)</f>
         <v/>
       </c>
       <c r="V62" s="97">
-        <f>SUM(R61:U61)</f>
+        <f>SUM(R62:U62)</f>
         <v/>
       </c>
     </row>
@@ -7682,7 +7675,7 @@
       <c r="B63" s="20" t="n"/>
       <c r="C63" s="39" t="n"/>
       <c r="D63" s="97">
-        <f>SUM(E62:P62)</f>
+        <f>SUM(E63:P63)</f>
         <v/>
       </c>
       <c r="E63" s="39" t="n"/>
@@ -7699,23 +7692,23 @@
       <c r="P63" s="39" t="n"/>
       <c r="Q63" s="18" t="n"/>
       <c r="R63" s="97">
-        <f>SUM(E62:G62)</f>
+        <f>SUM(E63:G63)</f>
         <v/>
       </c>
       <c r="S63" s="98">
-        <f>SUM(H62:J62)</f>
+        <f>SUM(H63:J63)</f>
         <v/>
       </c>
       <c r="T63" s="97">
-        <f>SUM(K62:M62)</f>
+        <f>SUM(K63:M63)</f>
         <v/>
       </c>
       <c r="U63" s="97">
-        <f>SUM(N62:P62)</f>
+        <f>SUM(N63:P63)</f>
         <v/>
       </c>
       <c r="V63" s="97">
-        <f>SUM(R62:U62)</f>
+        <f>SUM(R63:U63)</f>
         <v/>
       </c>
     </row>
@@ -7723,7 +7716,7 @@
       <c r="B64" s="20" t="n"/>
       <c r="C64" s="39" t="n"/>
       <c r="D64" s="97">
-        <f>SUM(E63:P63)</f>
+        <f>SUM(E64:P64)</f>
         <v/>
       </c>
       <c r="E64" s="39" t="n"/>
@@ -7740,120 +7733,79 @@
       <c r="P64" s="39" t="n"/>
       <c r="Q64" s="18" t="n"/>
       <c r="R64" s="97">
-        <f>SUM(E63:G63)</f>
+        <f>SUM(E64:G64)</f>
         <v/>
       </c>
       <c r="S64" s="98">
-        <f>SUM(H63:J63)</f>
+        <f>SUM(H64:J64)</f>
         <v/>
       </c>
       <c r="T64" s="97">
-        <f>SUM(K63:M63)</f>
+        <f>SUM(K64:M64)</f>
         <v/>
       </c>
       <c r="U64" s="97">
-        <f>SUM(N63:P63)</f>
+        <f>SUM(N64:P64)</f>
         <v/>
       </c>
       <c r="V64" s="97">
-        <f>SUM(R63:U63)</f>
+        <f>SUM(R64:U64)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="20" t="n"/>
-      <c r="C65" s="39" t="n"/>
-      <c r="D65" s="97">
-        <f>SUM(E64:P64)</f>
-        <v/>
-      </c>
-      <c r="E65" s="39" t="n"/>
-      <c r="F65" s="39" t="n"/>
-      <c r="G65" s="39" t="n"/>
-      <c r="H65" s="39" t="n"/>
-      <c r="I65" s="39" t="n"/>
-      <c r="J65" s="39" t="n"/>
-      <c r="K65" s="39" t="n"/>
-      <c r="L65" s="39" t="n"/>
-      <c r="M65" s="39" t="n"/>
-      <c r="N65" s="39" t="n"/>
-      <c r="O65" s="39" t="n"/>
-      <c r="P65" s="39" t="n"/>
-      <c r="Q65" s="18" t="n"/>
-      <c r="R65" s="97">
-        <f>SUM(E64:G64)</f>
-        <v/>
-      </c>
-      <c r="S65" s="98">
-        <f>SUM(H64:J64)</f>
-        <v/>
-      </c>
-      <c r="T65" s="97">
-        <f>SUM(K64:M64)</f>
-        <v/>
-      </c>
-      <c r="U65" s="97">
-        <f>SUM(N64:P64)</f>
-        <v/>
-      </c>
-      <c r="V65" s="97">
-        <f>SUM(R64:U64)</f>
-        <v/>
-      </c>
+      <c r="A65" s="110" t="inlineStr">
+        <is>
+          <t>例</t>
+        </is>
+      </c>
+      <c r="B65" s="110" t="inlineStr">
+        <is>
+          <t>設備購入</t>
+        </is>
+      </c>
+      <c r="C65" s="110" t="inlineStr">
+        <is>
+          <t>AA装置、3台</t>
+        </is>
+      </c>
+      <c r="D65" s="110" t="n"/>
+      <c r="E65" s="110" t="n"/>
+      <c r="F65" s="110" t="n"/>
+      <c r="G65" s="110" t="n"/>
+      <c r="H65" s="110" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I65" s="110" t="n"/>
+      <c r="J65" s="110" t="n"/>
+      <c r="K65" s="53" t="n"/>
+      <c r="L65" s="53" t="n"/>
+      <c r="M65" s="53" t="n"/>
+      <c r="N65" s="53" t="n"/>
+      <c r="O65" s="53" t="n"/>
+      <c r="P65" s="53" t="n"/>
+      <c r="Q65" s="53" t="n"/>
+      <c r="R65" s="53" t="n"/>
+      <c r="S65" s="53" t="n"/>
+      <c r="T65" s="53" t="n"/>
+      <c r="U65" s="53" t="n"/>
+      <c r="V65" s="53" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="110" t="inlineStr">
-        <is>
-          <t>例</t>
-        </is>
-      </c>
-      <c r="B66" s="110" t="inlineStr">
-        <is>
-          <t>設備購入</t>
-        </is>
-      </c>
-      <c r="C66" s="110" t="inlineStr">
-        <is>
-          <t>AA装置、3台</t>
-        </is>
-      </c>
-      <c r="D66" s="110" t="n"/>
-      <c r="E66" s="110" t="n"/>
-      <c r="F66" s="110" t="n"/>
-      <c r="G66" s="110" t="n"/>
-      <c r="H66" s="110" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="I66" s="110" t="n"/>
-      <c r="J66" s="110" t="n"/>
-      <c r="K66" s="53" t="n"/>
-      <c r="L66" s="53" t="n"/>
-      <c r="M66" s="53" t="n"/>
-      <c r="N66" s="53" t="n"/>
-      <c r="O66" s="53" t="n"/>
-      <c r="P66" s="53" t="n"/>
-      <c r="Q66" s="53" t="n"/>
-      <c r="R66" s="53" t="n"/>
-      <c r="S66" s="53" t="n"/>
-      <c r="T66" s="53" t="n"/>
-      <c r="U66" s="53" t="n"/>
-      <c r="V66" s="53" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="121" t="n"/>
-      <c r="B67" s="121" t="inlineStr">
+      <c r="A66" s="121" t="n"/>
+      <c r="B66" s="121" t="inlineStr">
         <is>
           <t>★固定資産関連費（減価償却費、固定資産税、保険料）の月々の金額は、＜経費＞の欄に記載をしてください。こちらの設備投資は、購入金額、どのような資産を何台購入するかです。</t>
         </is>
       </c>
-      <c r="C67" s="121" t="n"/>
-      <c r="D67" s="121" t="n"/>
-      <c r="E67" s="121" t="n"/>
-      <c r="F67" s="121" t="n"/>
-      <c r="G67" s="121" t="n"/>
-      <c r="H67" s="121" t="n"/>
-      <c r="I67" s="121" t="n"/>
-      <c r="J67" s="121" t="n"/>
+      <c r="C66" s="121" t="n"/>
+      <c r="D66" s="121" t="n"/>
+      <c r="E66" s="121" t="n"/>
+      <c r="F66" s="121" t="n"/>
+      <c r="G66" s="121" t="n"/>
+      <c r="H66" s="121" t="n"/>
+      <c r="I66" s="121" t="n"/>
+      <c r="J66" s="121" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="P1w1NeOlUabrDApEg3OQXA==" formatRows="1" sort="1" spinCount="100000" hashValue="1cGxtXL4c7J8cIANrYPk7nA6FqC/XiEANbxtfnwBv8/G+3xIbbA3dGIYhccwzKKVmCaLvR5TSgRQ6sGUwasjMg=="/>
